--- a/Mecanica/m12bis_mecanica/m12bis.xlsx
+++ b/Mecanica/m12bis_mecanica/m12bis.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Andres\Desktop\fisica2\Mecanica y Ondas\practicas\m12bis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Andres\proyectos\Mecanica\m12bis_mecanica\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51E35EBF-0F04-4E2C-8D82-90BDDB1922EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FCAC022-0690-4A82-A90F-460D24120127}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{28493E50-620E-4A22-96F6-03B30C7A26DD}"/>
+    <workbookView xWindow="-28905" yWindow="0" windowWidth="19995" windowHeight="15225" xr2:uid="{28493E50-620E-4A22-96F6-03B30C7A26DD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,27 +36,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <t>#multi:</t>
   </si>
   <si>
-    <t>mass E</t>
-  </si>
-  <si>
-    <t>mass F</t>
-  </si>
-  <si>
     <t>t</t>
-  </si>
-  <si>
-    <t>x</t>
-  </si>
-  <si>
-    <t>y</t>
-  </si>
-  <si>
-    <t>v</t>
   </si>
   <si>
     <t>x0.6</t>
@@ -537,7 +522,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B717C263-EDFB-4213-9A1D-7296B35B4593}">
-  <dimension ref="A1:AK197"/>
+  <dimension ref="A1:AV197"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="9.21875" bestFit="1" customWidth="1"/>
@@ -545,120 +530,120 @@
     <col min="8" max="9" width="8.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" t="s">
+        <v>16</v>
+      </c>
+      <c r="L1" t="s">
         <v>7</v>
       </c>
-      <c r="C1" t="s">
+      <c r="M1" t="s">
         <v>17</v>
       </c>
-      <c r="D1" t="s">
+      <c r="N1" t="s">
         <v>8</v>
       </c>
-      <c r="E1" t="s">
+      <c r="O1" t="s">
         <v>18</v>
       </c>
-      <c r="F1" t="s">
+      <c r="P1" t="s">
         <v>9</v>
       </c>
-      <c r="G1" t="s">
+      <c r="Q1" t="s">
         <v>19</v>
       </c>
-      <c r="H1" t="s">
+      <c r="R1" t="s">
         <v>10</v>
       </c>
-      <c r="I1" t="s">
+      <c r="S1" t="s">
         <v>20</v>
       </c>
-      <c r="J1" t="s">
+      <c r="T1" t="s">
         <v>11</v>
       </c>
-      <c r="K1" t="s">
+      <c r="U1" t="s">
+        <v>29</v>
+      </c>
+      <c r="V1" t="s">
         <v>21</v>
       </c>
-      <c r="L1" t="s">
-        <v>12</v>
-      </c>
-      <c r="M1" t="s">
+      <c r="W1" t="s">
+        <v>30</v>
+      </c>
+      <c r="X1" t="s">
         <v>22</v>
       </c>
-      <c r="N1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" t="s">
+      <c r="Y1" t="s">
+        <v>31</v>
+      </c>
+      <c r="Z1" t="s">
         <v>23</v>
       </c>
-      <c r="P1" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q1" t="s">
+      <c r="AA1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB1" t="s">
         <v>24</v>
       </c>
-      <c r="R1" t="s">
-        <v>15</v>
-      </c>
-      <c r="S1" t="s">
+      <c r="AC1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AD1" t="s">
         <v>25</v>
       </c>
-      <c r="T1" t="s">
-        <v>16</v>
-      </c>
-      <c r="U1" t="s">
+      <c r="AE1" t="s">
         <v>34</v>
       </c>
-      <c r="V1" t="s">
+      <c r="AF1" t="s">
         <v>26</v>
       </c>
-      <c r="W1" t="s">
+      <c r="AG1" t="s">
         <v>35</v>
       </c>
-      <c r="X1" t="s">
+      <c r="AH1" t="s">
         <v>27</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AI1" t="s">
         <v>36</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AJ1" t="s">
         <v>28</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AK1" t="s">
         <v>37</v>
       </c>
-      <c r="AB1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>30</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AF1" t="s">
-        <v>31</v>
-      </c>
-      <c r="AG1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AH1" t="s">
-        <v>32</v>
-      </c>
-      <c r="AI1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AJ1" t="s">
-        <v>33</v>
-      </c>
-      <c r="AK1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:42" x14ac:dyDescent="0.3">
       <c r="C2">
         <f>0.01*B2</f>
         <v>0</v>
@@ -683,16 +668,10 @@
         <f>0.01*L2</f>
         <v>0</v>
       </c>
-      <c r="Z2" t="s">
+    </row>
+    <row r="3" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>1</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
       </c>
       <c r="C3">
         <f t="shared" ref="C3:C66" si="0">0.01*B3</f>
@@ -718,26 +697,8 @@
         <f t="shared" ref="M3:M66" si="5">0.01*L3</f>
         <v>0</v>
       </c>
-      <c r="Z3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>6</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>0.3833318</v>
       </c>
@@ -776,7 +737,7 @@
       </c>
       <c r="Q4" s="1"/>
     </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>0.39999839999999998</v>
       </c>
@@ -819,7 +780,7 @@
       </c>
       <c r="S5" s="1"/>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>0.41666500000000001</v>
       </c>
@@ -862,7 +823,7 @@
       </c>
       <c r="S6" s="1"/>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>0.43333159999999998</v>
       </c>
@@ -905,7 +866,7 @@
       </c>
       <c r="S7" s="1"/>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>0.44999820000000001</v>
       </c>
@@ -948,7 +909,7 @@
       </c>
       <c r="S8" s="1"/>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>0.46666479999999999</v>
       </c>
@@ -991,7 +952,7 @@
       </c>
       <c r="S9" s="1"/>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>0.48333140000000002</v>
       </c>
@@ -1034,7 +995,7 @@
       </c>
       <c r="S10" s="1"/>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>0.499998</v>
       </c>
@@ -1077,7 +1038,7 @@
       </c>
       <c r="S11" s="1"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>0.51666460000000003</v>
       </c>
@@ -1120,7 +1081,7 @@
       </c>
       <c r="S12" s="1"/>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>0.53333120000000001</v>
       </c>
@@ -1162,8 +1123,14 @@
         <v>19.276599999999998</v>
       </c>
       <c r="S13" s="1"/>
-    </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="AO13">
+        <v>4.5519999999999996</v>
+      </c>
+      <c r="AP13">
+        <v>-5.1959999999999997</v>
+      </c>
+    </row>
+    <row r="14" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>0.54999779999999998</v>
       </c>
@@ -1205,8 +1172,17 @@
         <v>20.20919</v>
       </c>
       <c r="S14" s="1"/>
-    </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="AJ14">
+        <v>0.73299999999999998</v>
+      </c>
+      <c r="AO14">
+        <v>4.5679999999999996</v>
+      </c>
+      <c r="AP14">
+        <v>-5.0359999999999996</v>
+      </c>
+    </row>
+    <row r="15" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>0.56666439999999996</v>
       </c>
@@ -1248,8 +1224,17 @@
         <v>20.470949999999998</v>
       </c>
       <c r="S15" s="1"/>
-    </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="AJ15">
+        <v>0.75</v>
+      </c>
+      <c r="AO15">
+        <v>4.577</v>
+      </c>
+      <c r="AP15">
+        <v>-4.8550000000000004</v>
+      </c>
+    </row>
+    <row r="16" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>0.58333100000000004</v>
       </c>
@@ -1291,8 +1276,17 @@
         <v>19.47852</v>
       </c>
       <c r="S16" s="1"/>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="AJ16">
+        <v>0.76700000000000002</v>
+      </c>
+      <c r="AO16">
+        <v>4.5880000000000001</v>
+      </c>
+      <c r="AP16">
+        <v>-4.681</v>
+      </c>
+    </row>
+    <row r="17" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>0.59999760000000002</v>
       </c>
@@ -1334,8 +1328,23 @@
         <v>20.37875</v>
       </c>
       <c r="S17" s="1"/>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="AJ17">
+        <v>0.78300000000000003</v>
+      </c>
+      <c r="AK17">
+        <v>4.5110000000000001</v>
+      </c>
+      <c r="AL17">
+        <v>-9.141</v>
+      </c>
+      <c r="AO17">
+        <v>4.5910000000000002</v>
+      </c>
+      <c r="AP17">
+        <v>-4.524</v>
+      </c>
+    </row>
+    <row r="18" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>0.6166642</v>
       </c>
@@ -1377,8 +1386,23 @@
         <v>20.044139999999999</v>
       </c>
       <c r="S18" s="1"/>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="AJ18">
+        <v>0.8</v>
+      </c>
+      <c r="AK18">
+        <v>4.5140000000000002</v>
+      </c>
+      <c r="AL18">
+        <v>-9.0169999999999995</v>
+      </c>
+      <c r="AO18">
+        <v>4.5990000000000002</v>
+      </c>
+      <c r="AP18">
+        <v>-4.3419999999999996</v>
+      </c>
+    </row>
+    <row r="19" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>0.63333079999999997</v>
       </c>
@@ -1420,8 +1444,23 @@
         <v>19.32226</v>
       </c>
       <c r="S19" s="1"/>
-    </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="AJ19">
+        <v>0.81699999999999995</v>
+      </c>
+      <c r="AK19">
+        <v>4.5179999999999998</v>
+      </c>
+      <c r="AL19">
+        <v>-8.8889999999999993</v>
+      </c>
+      <c r="AO19">
+        <v>4.6059999999999999</v>
+      </c>
+      <c r="AP19">
+        <v>-4.1630000000000003</v>
+      </c>
+    </row>
+    <row r="20" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>0.64999739999999995</v>
       </c>
@@ -1463,8 +1502,23 @@
         <v>19.852450000000001</v>
       </c>
       <c r="S20" s="1"/>
-    </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="AJ20">
+        <v>0.83299999999999996</v>
+      </c>
+      <c r="AK20">
+        <v>4.5179999999999998</v>
+      </c>
+      <c r="AL20">
+        <v>-8.7170000000000005</v>
+      </c>
+      <c r="AO20">
+        <v>4.6059999999999999</v>
+      </c>
+      <c r="AP20">
+        <v>-3.9990000000000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>0.66666400000000003</v>
       </c>
@@ -1506,8 +1560,23 @@
         <v>18.03669</v>
       </c>
       <c r="S21" s="1"/>
-    </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="AJ21">
+        <v>0.85</v>
+      </c>
+      <c r="AK21">
+        <v>4.5250000000000004</v>
+      </c>
+      <c r="AL21">
+        <v>-8.5510000000000002</v>
+      </c>
+      <c r="AO21">
+        <v>4.6079999999999997</v>
+      </c>
+      <c r="AP21">
+        <v>-3.8130000000000002</v>
+      </c>
+    </row>
+    <row r="22" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>0.68333060000000001</v>
       </c>
@@ -1549,8 +1618,23 @@
         <v>16.76613</v>
       </c>
       <c r="S22" s="1"/>
-    </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="AJ22">
+        <v>0.86699999999999999</v>
+      </c>
+      <c r="AK22">
+        <v>4.5220000000000002</v>
+      </c>
+      <c r="AL22">
+        <v>-8.4030000000000005</v>
+      </c>
+      <c r="AO22">
+        <v>4.609</v>
+      </c>
+      <c r="AP22">
+        <v>-3.637</v>
+      </c>
+    </row>
+    <row r="23" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>0.69999719999999999</v>
       </c>
@@ -1592,8 +1676,23 @@
         <v>17.75977</v>
       </c>
       <c r="S23" s="1"/>
-    </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="AJ23">
+        <v>0.88300000000000001</v>
+      </c>
+      <c r="AK23">
+        <v>4.5179999999999998</v>
+      </c>
+      <c r="AL23">
+        <v>-8.2319999999999993</v>
+      </c>
+      <c r="AO23">
+        <v>4.6070000000000002</v>
+      </c>
+      <c r="AP23">
+        <v>-3.4729999999999999</v>
+      </c>
+    </row>
+    <row r="24" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>0.71666379999999996</v>
       </c>
@@ -1635,8 +1734,23 @@
         <v>17.266690000000001</v>
       </c>
       <c r="S24" s="1"/>
-    </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="AJ24">
+        <v>0.9</v>
+      </c>
+      <c r="AK24">
+        <v>4.5170000000000003</v>
+      </c>
+      <c r="AL24">
+        <v>-8.0760000000000005</v>
+      </c>
+      <c r="AO24">
+        <v>4.609</v>
+      </c>
+      <c r="AP24">
+        <v>-3.282</v>
+      </c>
+    </row>
+    <row r="25" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>0.73333040000000005</v>
       </c>
@@ -1678,8 +1792,23 @@
         <v>17.476400000000002</v>
       </c>
       <c r="S25" s="1"/>
-    </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="AJ25">
+        <v>0.91700000000000004</v>
+      </c>
+      <c r="AK25">
+        <v>4.5170000000000003</v>
+      </c>
+      <c r="AL25">
+        <v>-7.9219999999999997</v>
+      </c>
+      <c r="AO25">
+        <v>4.609</v>
+      </c>
+      <c r="AP25">
+        <v>-3.1019999999999999</v>
+      </c>
+    </row>
+    <row r="26" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>0.74999700000000002</v>
       </c>
@@ -1721,8 +1850,23 @@
         <v>18.183199999999999</v>
       </c>
       <c r="S26" s="1"/>
-    </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="AJ26">
+        <v>0.93300000000000005</v>
+      </c>
+      <c r="AK26">
+        <v>4.5170000000000003</v>
+      </c>
+      <c r="AL26">
+        <v>-7.7549999999999999</v>
+      </c>
+      <c r="AO26">
+        <v>4.6050000000000004</v>
+      </c>
+      <c r="AP26">
+        <v>-2.9460000000000002</v>
+      </c>
+    </row>
+    <row r="27" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>0.7666636</v>
       </c>
@@ -1764,8 +1908,23 @@
         <v>16.99071</v>
       </c>
       <c r="S27" s="1"/>
-    </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="AJ27">
+        <v>0.95</v>
+      </c>
+      <c r="AK27">
+        <v>4.5170000000000003</v>
+      </c>
+      <c r="AL27">
+        <v>-7.5979999999999999</v>
+      </c>
+      <c r="AO27">
+        <v>4.601</v>
+      </c>
+      <c r="AP27">
+        <v>-2.7589999999999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>0.78333019999999998</v>
       </c>
@@ -1813,8 +1972,23 @@
         <v>17.367249999999999</v>
       </c>
       <c r="S28" s="1"/>
-    </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="AJ28">
+        <v>0.96699999999999997</v>
+      </c>
+      <c r="AK28">
+        <v>4.516</v>
+      </c>
+      <c r="AL28">
+        <v>-7.4420000000000002</v>
+      </c>
+      <c r="AO28">
+        <v>4.6040000000000001</v>
+      </c>
+      <c r="AP28">
+        <v>-2.5859999999999999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>0.79999679999999995</v>
       </c>
@@ -1865,8 +2039,23 @@
         <v>18.484279999999998</v>
       </c>
       <c r="S29" s="1"/>
-    </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="AJ29">
+        <v>0.98299999999999998</v>
+      </c>
+      <c r="AK29">
+        <v>4.5170000000000003</v>
+      </c>
+      <c r="AL29">
+        <v>-7.2779999999999996</v>
+      </c>
+      <c r="AO29">
+        <v>4.6040000000000001</v>
+      </c>
+      <c r="AP29">
+        <v>-2.423</v>
+      </c>
+    </row>
+    <row r="30" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>0.81666340000000004</v>
       </c>
@@ -1917,8 +2106,23 @@
         <v>17.53914</v>
       </c>
       <c r="S30" s="1"/>
-    </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="AJ30">
+        <v>1</v>
+      </c>
+      <c r="AK30">
+        <v>4.5170000000000003</v>
+      </c>
+      <c r="AL30">
+        <v>-7.1269999999999998</v>
+      </c>
+      <c r="AO30">
+        <v>4.6079999999999997</v>
+      </c>
+      <c r="AP30">
+        <v>-2.2370000000000001</v>
+      </c>
+    </row>
+    <row r="31" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>0.83333000000000002</v>
       </c>
@@ -1969,8 +2173,23 @@
         <v>17.898489999999999</v>
       </c>
       <c r="S31" s="1"/>
-    </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="AJ31">
+        <v>1.0169999999999999</v>
+      </c>
+      <c r="AK31">
+        <v>4.5199999999999996</v>
+      </c>
+      <c r="AL31">
+        <v>-6.9740000000000002</v>
+      </c>
+      <c r="AO31">
+        <v>4.6100000000000003</v>
+      </c>
+      <c r="AP31">
+        <v>-2.0739999999999998</v>
+      </c>
+    </row>
+    <row r="32" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>0.84999659999999999</v>
       </c>
@@ -2021,8 +2240,23 @@
         <v>18.54243</v>
       </c>
       <c r="S32" s="1"/>
-    </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="AJ32">
+        <v>1.0329999999999999</v>
+      </c>
+      <c r="AK32">
+        <v>4.516</v>
+      </c>
+      <c r="AL32">
+        <v>-6.8090000000000002</v>
+      </c>
+      <c r="AO32">
+        <v>4.6159999999999997</v>
+      </c>
+      <c r="AP32">
+        <v>-1.915</v>
+      </c>
+    </row>
+    <row r="33" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>0.86666319999999997</v>
       </c>
@@ -2073,8 +2307,23 @@
         <v>17.416689999999999</v>
       </c>
       <c r="S33" s="1"/>
-    </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="AJ33">
+        <v>1.05</v>
+      </c>
+      <c r="AK33">
+        <v>4.5140000000000002</v>
+      </c>
+      <c r="AL33">
+        <v>-6.6639999999999997</v>
+      </c>
+      <c r="AO33">
+        <v>4.6289999999999996</v>
+      </c>
+      <c r="AP33">
+        <v>-1.738</v>
+      </c>
+    </row>
+    <row r="34" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>0.88332980000000005</v>
       </c>
@@ -2125,8 +2374,23 @@
         <v>18.16751</v>
       </c>
       <c r="S34" s="1"/>
-    </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="AJ34">
+        <v>1.0669999999999999</v>
+      </c>
+      <c r="AK34">
+        <v>4.5140000000000002</v>
+      </c>
+      <c r="AL34">
+        <v>-6.5119999999999996</v>
+      </c>
+      <c r="AO34">
+        <v>4.6390000000000002</v>
+      </c>
+      <c r="AP34">
+        <v>-1.583</v>
+      </c>
+    </row>
+    <row r="35" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>0.89999640000000003</v>
       </c>
@@ -2177,8 +2441,23 @@
         <v>18.984390000000001</v>
       </c>
       <c r="S35" s="1"/>
-    </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="AJ35">
+        <v>1.083</v>
+      </c>
+      <c r="AK35">
+        <v>4.5140000000000002</v>
+      </c>
+      <c r="AL35">
+        <v>-6.3449999999999998</v>
+      </c>
+      <c r="AO35">
+        <v>4.6520000000000001</v>
+      </c>
+      <c r="AP35">
+        <v>-1.421</v>
+      </c>
+    </row>
+    <row r="36" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>0.91666300000000001</v>
       </c>
@@ -2229,8 +2508,23 @@
         <v>17.198239999999998</v>
       </c>
       <c r="S36" s="1"/>
-    </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="AJ36">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AK36">
+        <v>4.5170000000000003</v>
+      </c>
+      <c r="AL36">
+        <v>-6.2050000000000001</v>
+      </c>
+      <c r="AO36">
+        <v>4.6749999999999998</v>
+      </c>
+      <c r="AP36">
+        <v>-1.2509999999999999</v>
+      </c>
+    </row>
+    <row r="37" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>0.93332959999999998</v>
       </c>
@@ -2281,8 +2575,23 @@
         <v>17.51399</v>
       </c>
       <c r="S37" s="1"/>
-    </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="AJ37">
+        <v>1.117</v>
+      </c>
+      <c r="AK37">
+        <v>4.516</v>
+      </c>
+      <c r="AL37">
+        <v>-6.0510000000000002</v>
+      </c>
+      <c r="AO37">
+        <v>4.6970000000000001</v>
+      </c>
+      <c r="AP37">
+        <v>-1.099</v>
+      </c>
+    </row>
+    <row r="38" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>0.94999619999999996</v>
       </c>
@@ -2333,8 +2642,23 @@
         <v>18.399529999999999</v>
       </c>
       <c r="S38" s="1"/>
-    </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="AJ38">
+        <v>1.133</v>
+      </c>
+      <c r="AK38">
+        <v>4.5140000000000002</v>
+      </c>
+      <c r="AL38">
+        <v>-5.8920000000000003</v>
+      </c>
+      <c r="AO38">
+        <v>4.7240000000000002</v>
+      </c>
+      <c r="AP38">
+        <v>-0.93899999999999995</v>
+      </c>
+    </row>
+    <row r="39" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>0.96666280000000004</v>
       </c>
@@ -2385,8 +2709,23 @@
         <v>17.19528</v>
       </c>
       <c r="S39" s="1"/>
-    </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="AJ39">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="AK39">
+        <v>4.5149999999999997</v>
+      </c>
+      <c r="AL39">
+        <v>-5.7539999999999996</v>
+      </c>
+      <c r="AO39">
+        <v>4.7519999999999998</v>
+      </c>
+      <c r="AP39">
+        <v>-0.77200000000000002</v>
+      </c>
+    </row>
+    <row r="40" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>0.98332940000000002</v>
       </c>
@@ -2437,8 +2776,23 @@
         <v>17.85033</v>
       </c>
       <c r="S40" s="1"/>
-    </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="AJ40">
+        <v>1.167</v>
+      </c>
+      <c r="AK40">
+        <v>4.5279999999999996</v>
+      </c>
+      <c r="AL40">
+        <v>-5.6219999999999999</v>
+      </c>
+      <c r="AO40">
+        <v>4.7779999999999996</v>
+      </c>
+      <c r="AP40">
+        <v>-0.625</v>
+      </c>
+    </row>
+    <row r="41" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>0.999996</v>
       </c>
@@ -2489,8 +2843,23 @@
         <v>17.869630000000001</v>
       </c>
       <c r="S41" s="1"/>
-    </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="AJ41">
+        <v>1.1830000000000001</v>
+      </c>
+      <c r="AK41">
+        <v>4.5460000000000003</v>
+      </c>
+      <c r="AL41">
+        <v>-5.4980000000000002</v>
+      </c>
+      <c r="AO41">
+        <v>4.8170000000000002</v>
+      </c>
+      <c r="AP41">
+        <v>-0.46</v>
+      </c>
+    </row>
+    <row r="42" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>1.0166630000000001</v>
       </c>
@@ -2541,8 +2910,23 @@
         <v>16.511759999999999</v>
       </c>
       <c r="S42" s="1"/>
-    </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="AJ42">
+        <v>1.2</v>
+      </c>
+      <c r="AK42">
+        <v>4.5599999999999996</v>
+      </c>
+      <c r="AL42">
+        <v>-5.3869999999999996</v>
+      </c>
+      <c r="AO42">
+        <v>4.8520000000000003</v>
+      </c>
+      <c r="AP42">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>1.0333289999999999</v>
       </c>
@@ -2593,8 +2977,23 @@
         <v>17.263120000000001</v>
       </c>
       <c r="S43" s="1"/>
-    </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="AJ43">
+        <v>1.2170000000000001</v>
+      </c>
+      <c r="AK43">
+        <v>4.5789999999999997</v>
+      </c>
+      <c r="AL43">
+        <v>-5.2569999999999997</v>
+      </c>
+      <c r="AO43">
+        <v>4.8890000000000002</v>
+      </c>
+      <c r="AP43">
+        <v>-0.16500000000000001</v>
+      </c>
+    </row>
+    <row r="44" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>1.0499959999999999</v>
       </c>
@@ -2645,8 +3044,23 @@
         <v>17.02495</v>
       </c>
       <c r="S44" s="1"/>
-    </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="AJ44">
+        <v>1.2330000000000001</v>
+      </c>
+      <c r="AK44">
+        <v>4.5910000000000002</v>
+      </c>
+      <c r="AL44">
+        <v>-5.1210000000000004</v>
+      </c>
+      <c r="AO44">
+        <v>4.9359999999999999</v>
+      </c>
+      <c r="AP44" s="1">
+        <v>5.1710000000000002E-3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>1.066662</v>
       </c>
@@ -2697,8 +3111,23 @@
         <v>16.215810000000001</v>
       </c>
       <c r="S45" s="1"/>
-    </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="AJ45">
+        <v>1.25</v>
+      </c>
+      <c r="AK45">
+        <v>4.5990000000000002</v>
+      </c>
+      <c r="AL45">
+        <v>-5.0069999999999997</v>
+      </c>
+      <c r="AO45">
+        <v>4.9790000000000001</v>
+      </c>
+      <c r="AP45">
+        <v>0.16200000000000001</v>
+      </c>
+    </row>
+    <row r="46" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>1.083329</v>
       </c>
@@ -2749,8 +3178,23 @@
         <v>17.094650000000001</v>
       </c>
       <c r="S46" s="1"/>
-    </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="AJ46">
+        <v>1.2669999999999999</v>
+      </c>
+      <c r="AK46">
+        <v>4.609</v>
+      </c>
+      <c r="AL46">
+        <v>-4.8689999999999998</v>
+      </c>
+      <c r="AO46">
+        <v>5.0229999999999997</v>
+      </c>
+      <c r="AP46">
+        <v>0.29899999999999999</v>
+      </c>
+    </row>
+    <row r="47" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>1.099996</v>
       </c>
@@ -2801,8 +3245,23 @@
         <v>16.646899999999999</v>
       </c>
       <c r="S47" s="1"/>
-    </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="AJ47">
+        <v>1.2829999999999999</v>
+      </c>
+      <c r="AK47">
+        <v>4.6120000000000001</v>
+      </c>
+      <c r="AL47">
+        <v>-4.7290000000000001</v>
+      </c>
+      <c r="AO47">
+        <v>5.077</v>
+      </c>
+      <c r="AP47">
+        <v>0.47099999999999997</v>
+      </c>
+    </row>
+    <row r="48" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>1.116662</v>
       </c>
@@ -2853,8 +3312,23 @@
         <v>16.164290000000001</v>
       </c>
       <c r="S48" s="1"/>
-    </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="AJ48">
+        <v>1.3</v>
+      </c>
+      <c r="AK48">
+        <v>4.6139999999999999</v>
+      </c>
+      <c r="AL48">
+        <v>-4.6050000000000004</v>
+      </c>
+      <c r="AO48">
+        <v>5.1230000000000002</v>
+      </c>
+      <c r="AP48">
+        <v>0.628</v>
+      </c>
+    </row>
+    <row r="49" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>1.133329</v>
       </c>
@@ -2905,8 +3379,23 @@
         <v>16.969799999999999</v>
       </c>
       <c r="S49" s="1"/>
-    </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="AJ49">
+        <v>1.3169999999999999</v>
+      </c>
+      <c r="AK49">
+        <v>4.6139999999999999</v>
+      </c>
+      <c r="AL49">
+        <v>-4.4649999999999999</v>
+      </c>
+      <c r="AO49">
+        <v>5.173</v>
+      </c>
+      <c r="AP49">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="50" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>1.1499950000000001</v>
       </c>
@@ -2957,8 +3446,23 @@
         <v>16.29421</v>
       </c>
       <c r="S50" s="1"/>
-    </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="AJ50">
+        <v>1.333</v>
+      </c>
+      <c r="AK50">
+        <v>4.6139999999999999</v>
+      </c>
+      <c r="AL50">
+        <v>-4.3280000000000003</v>
+      </c>
+      <c r="AO50">
+        <v>5.2270000000000003</v>
+      </c>
+      <c r="AP50">
+        <v>0.92500000000000004</v>
+      </c>
+    </row>
+    <row r="51" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>1.1666620000000001</v>
       </c>
@@ -3009,8 +3513,23 @@
         <v>16.31766</v>
       </c>
       <c r="S51" s="1"/>
-    </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="AJ51">
+        <v>1.35</v>
+      </c>
+      <c r="AK51">
+        <v>4.6139999999999999</v>
+      </c>
+      <c r="AL51">
+        <v>-4.2009999999999996</v>
+      </c>
+      <c r="AO51">
+        <v>5.2789999999999999</v>
+      </c>
+      <c r="AP51">
+        <v>1.083</v>
+      </c>
+    </row>
+    <row r="52" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>1.1833290000000001</v>
       </c>
@@ -3057,8 +3576,23 @@
         <v>17.05217</v>
       </c>
       <c r="S52" s="1"/>
-    </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="AJ52">
+        <v>1.367</v>
+      </c>
+      <c r="AK52">
+        <v>4.6130000000000004</v>
+      </c>
+      <c r="AL52">
+        <v>-4.0579999999999998</v>
+      </c>
+      <c r="AO52">
+        <v>5.3230000000000004</v>
+      </c>
+      <c r="AP52">
+        <v>1.2250000000000001</v>
+      </c>
+    </row>
+    <row r="53" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>1.1999949999999999</v>
       </c>
@@ -3105,8 +3639,23 @@
         <v>15.54848</v>
       </c>
       <c r="S53" s="1"/>
-    </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="AJ53">
+        <v>1.383</v>
+      </c>
+      <c r="AK53">
+        <v>4.609</v>
+      </c>
+      <c r="AL53">
+        <v>-3.9220000000000002</v>
+      </c>
+      <c r="AO53">
+        <v>5.38</v>
+      </c>
+      <c r="AP53">
+        <v>1.3919999999999999</v>
+      </c>
+    </row>
+    <row r="54" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>1.2166619999999999</v>
       </c>
@@ -3153,8 +3702,23 @@
         <v>16.199010000000001</v>
       </c>
       <c r="S54" s="1"/>
-    </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="AJ54">
+        <v>1.4</v>
+      </c>
+      <c r="AK54">
+        <v>4.6079999999999997</v>
+      </c>
+      <c r="AL54">
+        <v>-3.7970000000000002</v>
+      </c>
+      <c r="AO54">
+        <v>5.4219999999999997</v>
+      </c>
+      <c r="AP54">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="55" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>1.233328</v>
       </c>
@@ -3201,8 +3765,23 @@
         <v>17.361139999999999</v>
       </c>
       <c r="S55" s="1"/>
-    </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="AJ55">
+        <v>1.417</v>
+      </c>
+      <c r="AK55">
+        <v>4.5949999999999998</v>
+      </c>
+      <c r="AL55">
+        <v>-3.645</v>
+      </c>
+      <c r="AO55">
+        <v>5.4729999999999999</v>
+      </c>
+      <c r="AP55">
+        <v>1.6859999999999999</v>
+      </c>
+    </row>
+    <row r="56" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>1.249995</v>
       </c>
@@ -3249,8 +3828,23 @@
         <v>15.69003</v>
       </c>
       <c r="S56" s="1"/>
-    </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="AJ56">
+        <v>1.4330000000000001</v>
+      </c>
+      <c r="AK56">
+        <v>4.5860000000000003</v>
+      </c>
+      <c r="AL56">
+        <v>-3.508</v>
+      </c>
+      <c r="AO56">
+        <v>5.5179999999999998</v>
+      </c>
+      <c r="AP56">
+        <v>1.849</v>
+      </c>
+    </row>
+    <row r="57" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>1.266662</v>
       </c>
@@ -3297,8 +3891,23 @@
         <v>16.592590000000001</v>
       </c>
       <c r="S57" s="1"/>
-    </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="AJ57">
+        <v>1.45</v>
+      </c>
+      <c r="AK57">
+        <v>4.5830000000000002</v>
+      </c>
+      <c r="AL57">
+        <v>-3.3809999999999998</v>
+      </c>
+      <c r="AO57">
+        <v>5.5570000000000004</v>
+      </c>
+      <c r="AP57">
+        <v>1.992</v>
+      </c>
+    </row>
+    <row r="58" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>1.283328</v>
       </c>
@@ -3345,8 +3954,23 @@
         <v>17.570440000000001</v>
       </c>
       <c r="S58" s="1"/>
-    </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="AJ58">
+        <v>1.4670000000000001</v>
+      </c>
+      <c r="AK58">
+        <v>4.577</v>
+      </c>
+      <c r="AL58">
+        <v>-3.2349999999999999</v>
+      </c>
+      <c r="AO58">
+        <v>5.6</v>
+      </c>
+      <c r="AP58">
+        <v>2.1419999999999999</v>
+      </c>
+    </row>
+    <row r="59" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>1.299995</v>
       </c>
@@ -3393,8 +4017,23 @@
         <v>16.055019999999999</v>
       </c>
       <c r="S59" s="1"/>
-    </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="AJ59">
+        <v>1.4830000000000001</v>
+      </c>
+      <c r="AK59">
+        <v>4.5739999999999998</v>
+      </c>
+      <c r="AL59">
+        <v>-3.1070000000000002</v>
+      </c>
+      <c r="AO59">
+        <v>5.6440000000000001</v>
+      </c>
+      <c r="AP59">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="60" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>1.3166610000000001</v>
       </c>
@@ -3441,8 +4080,23 @@
         <v>16.145060000000001</v>
       </c>
       <c r="S60" s="1"/>
-    </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="AJ60">
+        <v>1.5</v>
+      </c>
+      <c r="AK60">
+        <v>4.569</v>
+      </c>
+      <c r="AL60">
+        <v>-2.9750000000000001</v>
+      </c>
+      <c r="AO60">
+        <v>5.6740000000000004</v>
+      </c>
+      <c r="AP60">
+        <v>2.4329999999999998</v>
+      </c>
+    </row>
+    <row r="61" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>1.3333280000000001</v>
       </c>
@@ -3489,8 +4143,23 @@
         <v>16.894629999999999</v>
       </c>
       <c r="S61" s="1"/>
-    </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="AJ61">
+        <v>1.5169999999999999</v>
+      </c>
+      <c r="AK61">
+        <v>4.5609999999999999</v>
+      </c>
+      <c r="AL61">
+        <v>-2.8290000000000002</v>
+      </c>
+      <c r="AO61">
+        <v>5.7039999999999997</v>
+      </c>
+      <c r="AP61">
+        <v>2.5779999999999998</v>
+      </c>
+    </row>
+    <row r="62" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>1.3499950000000001</v>
       </c>
@@ -3537,8 +4206,23 @@
         <v>16.10596</v>
       </c>
       <c r="S62" s="1"/>
-    </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="AJ62">
+        <v>1.5329999999999999</v>
+      </c>
+      <c r="AK62">
+        <v>4.5519999999999996</v>
+      </c>
+      <c r="AL62">
+        <v>-2.702</v>
+      </c>
+      <c r="AO62">
+        <v>5.742</v>
+      </c>
+      <c r="AP62">
+        <v>2.7320000000000002</v>
+      </c>
+    </row>
+    <row r="63" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>1.3666609999999999</v>
       </c>
@@ -3585,8 +4269,23 @@
         <v>16.640560000000001</v>
       </c>
       <c r="S63" s="1"/>
-    </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="AJ63">
+        <v>1.55</v>
+      </c>
+      <c r="AK63">
+        <v>4.55</v>
+      </c>
+      <c r="AL63">
+        <v>-2.5680000000000001</v>
+      </c>
+      <c r="AO63">
+        <v>5.7610000000000001</v>
+      </c>
+      <c r="AP63">
+        <v>2.8650000000000002</v>
+      </c>
+    </row>
+    <row r="64" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>1.3833279999999999</v>
       </c>
@@ -3633,8 +4332,23 @@
         <v>16.912099999999999</v>
       </c>
       <c r="S64" s="1"/>
-    </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="AJ64">
+        <v>1.5669999999999999</v>
+      </c>
+      <c r="AK64">
+        <v>4.5490000000000004</v>
+      </c>
+      <c r="AL64">
+        <v>-2.4289999999999998</v>
+      </c>
+      <c r="AO64">
+        <v>5.7859999999999996</v>
+      </c>
+      <c r="AP64">
+        <v>3.0049999999999999</v>
+      </c>
+    </row>
+    <row r="65" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>1.399994</v>
       </c>
@@ -3681,8 +4395,23 @@
         <v>15.78647</v>
       </c>
       <c r="S65" s="1"/>
-    </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="AJ65">
+        <v>1.583</v>
+      </c>
+      <c r="AK65">
+        <v>4.5519999999999996</v>
+      </c>
+      <c r="AL65">
+        <v>-2.3039999999999998</v>
+      </c>
+      <c r="AO65">
+        <v>5.8129999999999997</v>
+      </c>
+      <c r="AP65">
+        <v>3.153</v>
+      </c>
+    </row>
+    <row r="66" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <v>1.4166609999999999</v>
       </c>
@@ -3729,8 +4458,23 @@
         <v>16.546890000000001</v>
       </c>
       <c r="S66" s="1"/>
-    </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="AJ66">
+        <v>1.6</v>
+      </c>
+      <c r="AK66">
+        <v>4.5549999999999997</v>
+      </c>
+      <c r="AL66">
+        <v>-2.1800000000000002</v>
+      </c>
+      <c r="AO66">
+        <v>5.8280000000000003</v>
+      </c>
+      <c r="AP66">
+        <v>3.2759999999999998</v>
+      </c>
+    </row>
+    <row r="67" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>1.4333279999999999</v>
       </c>
@@ -3777,8 +4521,23 @@
         <v>16.244980000000002</v>
       </c>
       <c r="S67" s="1"/>
-    </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="AJ67">
+        <v>1.617</v>
+      </c>
+      <c r="AK67">
+        <v>4.5659999999999998</v>
+      </c>
+      <c r="AL67">
+        <v>-2.0449999999999999</v>
+      </c>
+      <c r="AO67">
+        <v>5.8780000000000001</v>
+      </c>
+      <c r="AP67">
+        <v>3.415</v>
+      </c>
+    </row>
+    <row r="68" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <v>1.449994</v>
       </c>
@@ -3825,8 +4584,23 @@
         <v>15.56132</v>
       </c>
       <c r="S68" s="1"/>
-    </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="AJ68">
+        <v>1.633</v>
+      </c>
+      <c r="AK68">
+        <v>4.5739999999999998</v>
+      </c>
+      <c r="AL68">
+        <v>-1.9259999999999999</v>
+      </c>
+      <c r="AO68">
+        <v>5.8760000000000003</v>
+      </c>
+      <c r="AP68">
+        <v>3.552</v>
+      </c>
+    </row>
+    <row r="69" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>1.466661</v>
       </c>
@@ -3873,8 +4647,23 @@
         <v>16.395520000000001</v>
       </c>
       <c r="S69" s="1"/>
-    </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="AJ69">
+        <v>1.65</v>
+      </c>
+      <c r="AK69">
+        <v>4.5830000000000002</v>
+      </c>
+      <c r="AL69">
+        <v>-1.7949999999999999</v>
+      </c>
+      <c r="AO69">
+        <v>5.899</v>
+      </c>
+      <c r="AP69">
+        <v>3.6779999999999999</v>
+      </c>
+    </row>
+    <row r="70" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <v>1.4833270000000001</v>
       </c>
@@ -3921,8 +4710,23 @@
         <v>15.383050000000001</v>
       </c>
       <c r="S70" s="1"/>
-    </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="AJ70">
+        <v>1.667</v>
+      </c>
+      <c r="AK70">
+        <v>4.6029999999999998</v>
+      </c>
+      <c r="AL70">
+        <v>-1.673</v>
+      </c>
+      <c r="AO70">
+        <v>5.9279999999999999</v>
+      </c>
+      <c r="AP70">
+        <v>3.8220000000000001</v>
+      </c>
+    </row>
+    <row r="71" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
         <v>1.499994</v>
       </c>
@@ -3969,8 +4773,23 @@
         <v>14.557980000000001</v>
       </c>
       <c r="S71" s="1"/>
-    </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="AJ71">
+        <v>1.6830000000000001</v>
+      </c>
+      <c r="AK71">
+        <v>4.6139999999999999</v>
+      </c>
+      <c r="AL71">
+        <v>-1.5660000000000001</v>
+      </c>
+      <c r="AO71">
+        <v>5.9550000000000001</v>
+      </c>
+      <c r="AP71">
+        <v>3.968</v>
+      </c>
+    </row>
+    <row r="72" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>1.516661</v>
       </c>
@@ -4017,8 +4836,23 @@
         <v>15.6701</v>
       </c>
       <c r="S72" s="1"/>
-    </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="AJ72">
+        <v>1.7</v>
+      </c>
+      <c r="AK72">
+        <v>4.6369999999999996</v>
+      </c>
+      <c r="AL72">
+        <v>-1.44</v>
+      </c>
+      <c r="AO72">
+        <v>5.9820000000000002</v>
+      </c>
+      <c r="AP72">
+        <v>4.0910000000000002</v>
+      </c>
+    </row>
+    <row r="73" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
         <v>1.5333270000000001</v>
       </c>
@@ -4065,8 +4899,29 @@
         <v>14.966559999999999</v>
       </c>
       <c r="S73" s="1"/>
-    </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="AJ73">
+        <v>1.7170000000000001</v>
+      </c>
+      <c r="AK73">
+        <v>4.6619999999999999</v>
+      </c>
+      <c r="AL73">
+        <v>-1.3160000000000001</v>
+      </c>
+      <c r="AO73">
+        <v>6.0129999999999999</v>
+      </c>
+      <c r="AP73">
+        <v>4.2320000000000002</v>
+      </c>
+      <c r="AQ73">
+        <v>4.4720000000000004</v>
+      </c>
+      <c r="AR73">
+        <v>-8.9030000000000005</v>
+      </c>
+    </row>
+    <row r="74" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
         <v>1.5499940000000001</v>
       </c>
@@ -4113,8 +4968,29 @@
         <v>14.17427</v>
       </c>
       <c r="S74" s="1"/>
-    </row>
-    <row r="75" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="AJ74">
+        <v>1.7330000000000001</v>
+      </c>
+      <c r="AK74">
+        <v>4.6840000000000002</v>
+      </c>
+      <c r="AL74">
+        <v>-1.21</v>
+      </c>
+      <c r="AO74">
+        <v>6.04</v>
+      </c>
+      <c r="AP74">
+        <v>4.3719999999999999</v>
+      </c>
+      <c r="AQ74">
+        <v>4.4740000000000002</v>
+      </c>
+      <c r="AR74">
+        <v>-8.6969999999999992</v>
+      </c>
+    </row>
+    <row r="75" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
         <v>1.5666599999999999</v>
       </c>
@@ -4161,8 +5037,29 @@
         <v>14.95382</v>
       </c>
       <c r="S75" s="1"/>
-    </row>
-    <row r="76" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="AJ75">
+        <v>1.75</v>
+      </c>
+      <c r="AK75">
+        <v>4.7169999999999996</v>
+      </c>
+      <c r="AL75">
+        <v>-1.085</v>
+      </c>
+      <c r="AO75">
+        <v>6.0590000000000002</v>
+      </c>
+      <c r="AP75">
+        <v>4.4989999999999997</v>
+      </c>
+      <c r="AQ75">
+        <v>4.4770000000000003</v>
+      </c>
+      <c r="AR75">
+        <v>-8.4610000000000003</v>
+      </c>
+    </row>
+    <row r="76" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
         <v>1.5833269999999999</v>
       </c>
@@ -4209,8 +5106,29 @@
         <v>13.994999999999999</v>
       </c>
       <c r="S76" s="1"/>
-    </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="AJ76">
+        <v>1.7669999999999999</v>
+      </c>
+      <c r="AK76">
+        <v>4.75</v>
+      </c>
+      <c r="AL76">
+        <v>-0.96899999999999997</v>
+      </c>
+      <c r="AO76">
+        <v>6.0869999999999997</v>
+      </c>
+      <c r="AP76">
+        <v>4.6440000000000001</v>
+      </c>
+      <c r="AQ76">
+        <v>4.4770000000000003</v>
+      </c>
+      <c r="AR76">
+        <v>-8.2349999999999994</v>
+      </c>
+    </row>
+    <row r="77" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
         <v>1.5999939999999999</v>
       </c>
@@ -4257,8 +5175,29 @@
         <v>13.22678</v>
       </c>
       <c r="S77" s="1"/>
-    </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="AJ77">
+        <v>1.7829999999999999</v>
+      </c>
+      <c r="AK77">
+        <v>4.7839999999999998</v>
+      </c>
+      <c r="AL77">
+        <v>-0.86099999999999999</v>
+      </c>
+      <c r="AO77">
+        <v>6.1120000000000001</v>
+      </c>
+      <c r="AP77">
+        <v>4.7830000000000004</v>
+      </c>
+      <c r="AQ77">
+        <v>4.4779999999999998</v>
+      </c>
+      <c r="AR77">
+        <v>-8.0310000000000006</v>
+      </c>
+    </row>
+    <row r="78" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
         <v>1.61666</v>
       </c>
@@ -4305,8 +5244,29 @@
         <v>14.343059999999999</v>
       </c>
       <c r="S78" s="1"/>
-    </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="AJ78">
+        <v>1.8</v>
+      </c>
+      <c r="AK78">
+        <v>4.8209999999999997</v>
+      </c>
+      <c r="AL78">
+        <v>-0.74</v>
+      </c>
+      <c r="AO78">
+        <v>6.13</v>
+      </c>
+      <c r="AP78">
+        <v>4.9029999999999996</v>
+      </c>
+      <c r="AQ78">
+        <v>4.4790000000000001</v>
+      </c>
+      <c r="AR78">
+        <v>-7.7930000000000001</v>
+      </c>
+    </row>
+    <row r="79" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
         <v>1.633327</v>
       </c>
@@ -4353,8 +5313,29 @@
         <v>14.005570000000001</v>
       </c>
       <c r="S79" s="1"/>
-    </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="AJ79">
+        <v>1.8169999999999999</v>
+      </c>
+      <c r="AK79">
+        <v>4.8680000000000003</v>
+      </c>
+      <c r="AL79">
+        <v>-0.622</v>
+      </c>
+      <c r="AO79">
+        <v>6.1509999999999998</v>
+      </c>
+      <c r="AP79">
+        <v>5.0430000000000001</v>
+      </c>
+      <c r="AQ79">
+        <v>4.4770000000000003</v>
+      </c>
+      <c r="AR79">
+        <v>-7.57</v>
+      </c>
+    </row>
+    <row r="80" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
         <v>1.649993</v>
       </c>
@@ -4401,8 +5382,29 @@
         <v>14.083959999999999</v>
       </c>
       <c r="S80" s="1"/>
-    </row>
-    <row r="81" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="AJ80">
+        <v>1.833</v>
+      </c>
+      <c r="AK80">
+        <v>4.91</v>
+      </c>
+      <c r="AL80">
+        <v>-0.52500000000000002</v>
+      </c>
+      <c r="AO80">
+        <v>6.18</v>
+      </c>
+      <c r="AP80">
+        <v>5.1760000000000002</v>
+      </c>
+      <c r="AQ80">
+        <v>4.4740000000000002</v>
+      </c>
+      <c r="AR80">
+        <v>-7.3609999999999998</v>
+      </c>
+    </row>
+    <row r="81" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
         <v>1.66666</v>
       </c>
@@ -4449,8 +5451,29 @@
         <v>15.11952</v>
       </c>
       <c r="S81" s="1"/>
-    </row>
-    <row r="82" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="AJ81">
+        <v>1.85</v>
+      </c>
+      <c r="AK81">
+        <v>4.9550000000000001</v>
+      </c>
+      <c r="AL81">
+        <v>-0.40400000000000003</v>
+      </c>
+      <c r="AO81">
+        <v>6.1980000000000004</v>
+      </c>
+      <c r="AP81">
+        <v>5.3</v>
+      </c>
+      <c r="AQ81">
+        <v>4.4720000000000004</v>
+      </c>
+      <c r="AR81">
+        <v>-7.1289999999999996</v>
+      </c>
+    </row>
+    <row r="82" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
         <v>1.683327</v>
       </c>
@@ -4497,8 +5520,29 @@
         <v>14.054130000000001</v>
       </c>
       <c r="S82" s="1"/>
-    </row>
-    <row r="83" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="AJ82">
+        <v>1.867</v>
+      </c>
+      <c r="AK82">
+        <v>5.0090000000000003</v>
+      </c>
+      <c r="AL82">
+        <v>-0.29299999999999998</v>
+      </c>
+      <c r="AO82">
+        <v>6.2210000000000001</v>
+      </c>
+      <c r="AP82">
+        <v>5.4379999999999997</v>
+      </c>
+      <c r="AQ82">
+        <v>4.4690000000000003</v>
+      </c>
+      <c r="AR82">
+        <v>-6.92</v>
+      </c>
+    </row>
+    <row r="83" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A83" s="1">
         <v>1.6999930000000001</v>
       </c>
@@ -4545,8 +5589,29 @@
         <v>13.82991</v>
       </c>
       <c r="S83" s="1"/>
-    </row>
-    <row r="84" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="AJ83">
+        <v>1.883</v>
+      </c>
+      <c r="AK83">
+        <v>5.056</v>
+      </c>
+      <c r="AL83">
+        <v>-0.185</v>
+      </c>
+      <c r="AO83">
+        <v>6.2460000000000004</v>
+      </c>
+      <c r="AP83">
+        <v>5.5650000000000004</v>
+      </c>
+      <c r="AQ83">
+        <v>4.4710000000000001</v>
+      </c>
+      <c r="AR83">
+        <v>-6.7080000000000002</v>
+      </c>
+    </row>
+    <row r="84" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A84" s="1">
         <v>1.7166600000000001</v>
       </c>
@@ -4601,8 +5666,29 @@
         <v>-15.1875</v>
       </c>
       <c r="W84" s="1"/>
-    </row>
-    <row r="85" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="AJ84">
+        <v>1.9</v>
+      </c>
+      <c r="AK84">
+        <v>5.1159999999999997</v>
+      </c>
+      <c r="AL84" s="1">
+        <v>-6.4689999999999998E-2</v>
+      </c>
+      <c r="AO84">
+        <v>6.27</v>
+      </c>
+      <c r="AP84">
+        <v>5.6879999999999997</v>
+      </c>
+      <c r="AQ84">
+        <v>4.4710000000000001</v>
+      </c>
+      <c r="AR84">
+        <v>-6.4829999999999997</v>
+      </c>
+    </row>
+    <row r="85" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A85" s="1">
         <v>1.7333259999999999</v>
       </c>
@@ -4661,8 +5747,29 @@
         <v>22.632490000000001</v>
       </c>
       <c r="Y85" s="1"/>
-    </row>
-    <row r="86" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="AJ85">
+        <v>1.917</v>
+      </c>
+      <c r="AK85">
+        <v>5.1760000000000002</v>
+      </c>
+      <c r="AL85" s="1">
+        <v>4.5339999999999998E-2</v>
+      </c>
+      <c r="AO85">
+        <v>6.2919999999999998</v>
+      </c>
+      <c r="AP85">
+        <v>5.8259999999999996</v>
+      </c>
+      <c r="AQ85">
+        <v>4.4690000000000003</v>
+      </c>
+      <c r="AR85">
+        <v>-6.2789999999999999</v>
+      </c>
+    </row>
+    <row r="86" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A86" s="1">
         <v>1.7499929999999999</v>
       </c>
@@ -4721,8 +5828,23 @@
         <v>23.636310000000002</v>
       </c>
       <c r="Y86" s="1"/>
-    </row>
-    <row r="87" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="AJ86">
+        <v>1.9330000000000001</v>
+      </c>
+      <c r="AK86">
+        <v>5.226</v>
+      </c>
+      <c r="AL86">
+        <v>0.14699999999999999</v>
+      </c>
+      <c r="AQ86">
+        <v>4.4649999999999999</v>
+      </c>
+      <c r="AR86">
+        <v>-6.0659999999999998</v>
+      </c>
+    </row>
+    <row r="87" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A87" s="1">
         <v>1.7666599999999999</v>
       </c>
@@ -4781,8 +5903,23 @@
         <v>22.04064</v>
       </c>
       <c r="Y87" s="1"/>
-    </row>
-    <row r="88" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="AJ87">
+        <v>1.95</v>
+      </c>
+      <c r="AK87">
+        <v>5.2880000000000003</v>
+      </c>
+      <c r="AL87">
+        <v>0.26500000000000001</v>
+      </c>
+      <c r="AQ87">
+        <v>4.4630000000000001</v>
+      </c>
+      <c r="AR87">
+        <v>-5.8460000000000001</v>
+      </c>
+    </row>
+    <row r="88" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A88" s="1">
         <v>1.783326</v>
       </c>
@@ -4841,8 +5978,35 @@
         <v>22.66001</v>
       </c>
       <c r="Y88" s="1"/>
-    </row>
-    <row r="89" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="AJ88">
+        <v>1.9670000000000001</v>
+      </c>
+      <c r="AK88">
+        <v>5.3490000000000002</v>
+      </c>
+      <c r="AL88">
+        <v>0.371</v>
+      </c>
+      <c r="AM88">
+        <v>4.3529999999999998</v>
+      </c>
+      <c r="AN88">
+        <v>-9.8140000000000001</v>
+      </c>
+      <c r="AQ88">
+        <v>4.4660000000000002</v>
+      </c>
+      <c r="AR88">
+        <v>-5.657</v>
+      </c>
+      <c r="AS88">
+        <v>2.8889999999999998</v>
+      </c>
+      <c r="AT88">
+        <v>-8.8239999999999998</v>
+      </c>
+    </row>
+    <row r="89" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
         <v>1.799993</v>
       </c>
@@ -4901,8 +6065,35 @@
         <v>23.577159999999999</v>
       </c>
       <c r="Y89" s="1"/>
-    </row>
-    <row r="90" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="AJ89">
+        <v>1.9830000000000001</v>
+      </c>
+      <c r="AK89">
+        <v>5.4059999999999997</v>
+      </c>
+      <c r="AL89">
+        <v>0.47899999999999998</v>
+      </c>
+      <c r="AM89">
+        <v>4.3540000000000001</v>
+      </c>
+      <c r="AN89">
+        <v>-9.7059999999999995</v>
+      </c>
+      <c r="AQ89">
+        <v>4.4790000000000001</v>
+      </c>
+      <c r="AR89">
+        <v>-5.4619999999999997</v>
+      </c>
+      <c r="AS89">
+        <v>2.8940000000000001</v>
+      </c>
+      <c r="AT89">
+        <v>-8.5890000000000004</v>
+      </c>
+    </row>
+    <row r="90" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
         <v>1.816659</v>
       </c>
@@ -4961,8 +6152,35 @@
         <v>22.10981</v>
       </c>
       <c r="Y90" s="1"/>
-    </row>
-    <row r="91" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="AJ90">
+        <v>2</v>
+      </c>
+      <c r="AK90">
+        <v>5.4690000000000003</v>
+      </c>
+      <c r="AL90">
+        <v>0.59599999999999997</v>
+      </c>
+      <c r="AM90">
+        <v>4.3550000000000004</v>
+      </c>
+      <c r="AN90">
+        <v>-9.6039999999999992</v>
+      </c>
+      <c r="AQ90">
+        <v>4.4960000000000004</v>
+      </c>
+      <c r="AR90">
+        <v>-5.266</v>
+      </c>
+      <c r="AS90">
+        <v>2.8940000000000001</v>
+      </c>
+      <c r="AT90">
+        <v>-8.36</v>
+      </c>
+    </row>
+    <row r="91" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
         <v>1.833326</v>
       </c>
@@ -5021,8 +6239,35 @@
         <v>22.570070000000001</v>
       </c>
       <c r="Y91" s="1"/>
-    </row>
-    <row r="92" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="AJ91">
+        <v>2.0169999999999999</v>
+      </c>
+      <c r="AK91">
+        <v>5.5259999999999998</v>
+      </c>
+      <c r="AL91">
+        <v>0.70299999999999996</v>
+      </c>
+      <c r="AM91">
+        <v>4.359</v>
+      </c>
+      <c r="AN91">
+        <v>-9.4909999999999997</v>
+      </c>
+      <c r="AQ91">
+        <v>4.5039999999999996</v>
+      </c>
+      <c r="AR91">
+        <v>-5.0919999999999996</v>
+      </c>
+      <c r="AS91">
+        <v>2.9</v>
+      </c>
+      <c r="AT91">
+        <v>-8.1050000000000004</v>
+      </c>
+    </row>
+    <row r="92" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
         <v>1.849993</v>
       </c>
@@ -5081,8 +6326,41 @@
         <v>22.524850000000001</v>
       </c>
       <c r="Y92" s="1"/>
-    </row>
-    <row r="93" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="AJ92">
+        <v>2.0329999999999999</v>
+      </c>
+      <c r="AK92">
+        <v>5.5869999999999997</v>
+      </c>
+      <c r="AL92">
+        <v>0.81</v>
+      </c>
+      <c r="AM92">
+        <v>4.3630000000000004</v>
+      </c>
+      <c r="AN92">
+        <v>-9.3580000000000005</v>
+      </c>
+      <c r="AQ92">
+        <v>4.5119999999999996</v>
+      </c>
+      <c r="AR92">
+        <v>-4.8890000000000002</v>
+      </c>
+      <c r="AS92">
+        <v>2.9009999999999998</v>
+      </c>
+      <c r="AT92">
+        <v>-7.8789999999999996</v>
+      </c>
+      <c r="AU92">
+        <v>4.4720000000000004</v>
+      </c>
+      <c r="AV92">
+        <v>-8.8239999999999998</v>
+      </c>
+    </row>
+    <row r="93" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
         <v>1.8666590000000001</v>
       </c>
@@ -5141,8 +6419,41 @@
         <v>21.555710000000001</v>
       </c>
       <c r="Y93" s="1"/>
-    </row>
-    <row r="94" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="AJ93">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="AK93">
+        <v>5.649</v>
+      </c>
+      <c r="AL93">
+        <v>0.92400000000000004</v>
+      </c>
+      <c r="AM93">
+        <v>4.3620000000000001</v>
+      </c>
+      <c r="AN93">
+        <v>-9.2289999999999992</v>
+      </c>
+      <c r="AQ93">
+        <v>4.5199999999999996</v>
+      </c>
+      <c r="AR93">
+        <v>-4.6920000000000002</v>
+      </c>
+      <c r="AS93">
+        <v>2.9049999999999998</v>
+      </c>
+      <c r="AT93">
+        <v>-7.6440000000000001</v>
+      </c>
+      <c r="AU93">
+        <v>4.476</v>
+      </c>
+      <c r="AV93">
+        <v>-8.5779999999999994</v>
+      </c>
+    </row>
+    <row r="94" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A94" s="1">
         <v>1.8833260000000001</v>
       </c>
@@ -5201,8 +6512,41 @@
         <v>22.396889999999999</v>
       </c>
       <c r="Y94" s="1"/>
-    </row>
-    <row r="95" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="AJ94">
+        <v>2.0670000000000002</v>
+      </c>
+      <c r="AK94">
+        <v>5.6970000000000001</v>
+      </c>
+      <c r="AL94">
+        <v>1.03</v>
+      </c>
+      <c r="AM94">
+        <v>4.3650000000000002</v>
+      </c>
+      <c r="AN94">
+        <v>-9.093</v>
+      </c>
+      <c r="AQ94">
+        <v>4.5220000000000002</v>
+      </c>
+      <c r="AR94">
+        <v>-4.508</v>
+      </c>
+      <c r="AS94">
+        <v>2.9169999999999998</v>
+      </c>
+      <c r="AT94">
+        <v>-7.3819999999999997</v>
+      </c>
+      <c r="AU94">
+        <v>4.4740000000000002</v>
+      </c>
+      <c r="AV94">
+        <v>-8.3309999999999995</v>
+      </c>
+    </row>
+    <row r="95" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
         <v>1.8999919999999999</v>
       </c>
@@ -5261,8 +6605,41 @@
         <v>21.943639999999998</v>
       </c>
       <c r="Y95" s="1"/>
-    </row>
-    <row r="96" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="AJ95">
+        <v>2.0830000000000002</v>
+      </c>
+      <c r="AK95">
+        <v>5.7519999999999998</v>
+      </c>
+      <c r="AL95">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="AM95">
+        <v>4.3719999999999999</v>
+      </c>
+      <c r="AN95">
+        <v>-8.9320000000000004</v>
+      </c>
+      <c r="AQ95">
+        <v>4.53</v>
+      </c>
+      <c r="AR95">
+        <v>-4.3</v>
+      </c>
+      <c r="AS95">
+        <v>2.915</v>
+      </c>
+      <c r="AT95">
+        <v>-7.17</v>
+      </c>
+      <c r="AU95">
+        <v>4.4790000000000001</v>
+      </c>
+      <c r="AV95">
+        <v>-8.0540000000000003</v>
+      </c>
+    </row>
+    <row r="96" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
         <v>1.9166589999999999</v>
       </c>
@@ -5317,8 +6694,41 @@
         <v>21.348669999999998</v>
       </c>
       <c r="Y96" s="1"/>
-    </row>
-    <row r="97" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AJ96">
+        <v>2.1</v>
+      </c>
+      <c r="AK96">
+        <v>5.8090000000000002</v>
+      </c>
+      <c r="AL96">
+        <v>1.254</v>
+      </c>
+      <c r="AM96">
+        <v>4.3760000000000003</v>
+      </c>
+      <c r="AN96">
+        <v>-8.7780000000000005</v>
+      </c>
+      <c r="AQ96">
+        <v>4.5309999999999997</v>
+      </c>
+      <c r="AR96">
+        <v>-4.0990000000000002</v>
+      </c>
+      <c r="AS96">
+        <v>2.915</v>
+      </c>
+      <c r="AT96">
+        <v>-6.9349999999999996</v>
+      </c>
+      <c r="AU96">
+        <v>4.476</v>
+      </c>
+      <c r="AV96">
+        <v>-7.8090000000000002</v>
+      </c>
+    </row>
+    <row r="97" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A97" s="1">
         <v>1.9333260000000001</v>
       </c>
@@ -5367,8 +6777,41 @@
         <v>22.162700000000001</v>
       </c>
       <c r="Y97" s="1"/>
-    </row>
-    <row r="98" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AJ97">
+        <v>2.117</v>
+      </c>
+      <c r="AK97">
+        <v>5.8520000000000003</v>
+      </c>
+      <c r="AL97">
+        <v>1.357</v>
+      </c>
+      <c r="AM97">
+        <v>4.3810000000000002</v>
+      </c>
+      <c r="AN97">
+        <v>-8.61</v>
+      </c>
+      <c r="AQ97">
+        <v>4.5309999999999997</v>
+      </c>
+      <c r="AR97">
+        <v>-3.9180000000000001</v>
+      </c>
+      <c r="AS97">
+        <v>2.9180000000000001</v>
+      </c>
+      <c r="AT97">
+        <v>-6.68</v>
+      </c>
+      <c r="AU97">
+        <v>4.4800000000000004</v>
+      </c>
+      <c r="AV97">
+        <v>-7.5640000000000001</v>
+      </c>
+    </row>
+    <row r="98" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
         <v>1.9499919999999999</v>
       </c>
@@ -5417,8 +6860,41 @@
         <v>20.898859999999999</v>
       </c>
       <c r="Y98" s="1"/>
-    </row>
-    <row r="99" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AJ98">
+        <v>2.133</v>
+      </c>
+      <c r="AK98">
+        <v>5.899</v>
+      </c>
+      <c r="AL98">
+        <v>1.4590000000000001</v>
+      </c>
+      <c r="AM98">
+        <v>4.3819999999999997</v>
+      </c>
+      <c r="AN98">
+        <v>-8.4120000000000008</v>
+      </c>
+      <c r="AQ98">
+        <v>4.5330000000000004</v>
+      </c>
+      <c r="AR98">
+        <v>-3.7109999999999999</v>
+      </c>
+      <c r="AS98">
+        <v>2.92</v>
+      </c>
+      <c r="AT98">
+        <v>-6.4710000000000001</v>
+      </c>
+      <c r="AU98">
+        <v>4.4870000000000001</v>
+      </c>
+      <c r="AV98">
+        <v>-7.2960000000000003</v>
+      </c>
+    </row>
+    <row r="99" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
         <v>1.9666589999999999</v>
       </c>
@@ -5475,16 +6951,45 @@
         <v>19.669930000000001</v>
       </c>
       <c r="Y99" s="1"/>
-      <c r="Z99" s="1">
-        <v>4.9275000000000002</v>
-      </c>
+      <c r="Z99" s="1"/>
       <c r="AA99" s="1"/>
-      <c r="AB99" s="1">
-        <v>-15.0525</v>
-      </c>
+      <c r="AB99" s="1"/>
       <c r="AC99" s="1"/>
-    </row>
-    <row r="100" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AJ99">
+        <v>2.15</v>
+      </c>
+      <c r="AK99">
+        <v>5.9480000000000004</v>
+      </c>
+      <c r="AL99">
+        <v>1.57</v>
+      </c>
+      <c r="AM99">
+        <v>4.3810000000000002</v>
+      </c>
+      <c r="AN99">
+        <v>-8.2469999999999999</v>
+      </c>
+      <c r="AQ99">
+        <v>4.532</v>
+      </c>
+      <c r="AR99">
+        <v>-3.5169999999999999</v>
+      </c>
+      <c r="AS99">
+        <v>2.9289999999999998</v>
+      </c>
+      <c r="AT99">
+        <v>-6.2759999999999998</v>
+      </c>
+      <c r="AU99">
+        <v>4.4809999999999999</v>
+      </c>
+      <c r="AV99">
+        <v>-7.0679999999999996</v>
+      </c>
+    </row>
+    <row r="100" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
         <v>1.983325</v>
       </c>
@@ -5556,8 +7061,41 @@
         <v>23.787040000000001</v>
       </c>
       <c r="AE100" s="1"/>
-    </row>
-    <row r="101" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AJ100">
+        <v>2.1669999999999998</v>
+      </c>
+      <c r="AK100">
+        <v>5.9859999999999998</v>
+      </c>
+      <c r="AL100">
+        <v>1.669</v>
+      </c>
+      <c r="AM100">
+        <v>4.4409999999999998</v>
+      </c>
+      <c r="AN100">
+        <v>-8.0380000000000003</v>
+      </c>
+      <c r="AQ100">
+        <v>4.5339999999999998</v>
+      </c>
+      <c r="AR100">
+        <v>-3.335</v>
+      </c>
+      <c r="AS100">
+        <v>2.9489999999999998</v>
+      </c>
+      <c r="AT100">
+        <v>-6.06</v>
+      </c>
+      <c r="AU100">
+        <v>4.4880000000000004</v>
+      </c>
+      <c r="AV100">
+        <v>-6.8029999999999999</v>
+      </c>
+    </row>
+    <row r="101" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
         <v>1.999992</v>
       </c>
@@ -5629,8 +7167,41 @@
         <v>24.777670000000001</v>
       </c>
       <c r="AE101" s="1"/>
-    </row>
-    <row r="102" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AJ101">
+        <v>2.1829999999999998</v>
+      </c>
+      <c r="AK101">
+        <v>6.0279999999999996</v>
+      </c>
+      <c r="AL101">
+        <v>1.772</v>
+      </c>
+      <c r="AM101">
+        <v>4.3840000000000003</v>
+      </c>
+      <c r="AN101">
+        <v>-7.8819999999999997</v>
+      </c>
+      <c r="AQ101">
+        <v>4.53</v>
+      </c>
+      <c r="AR101">
+        <v>-3.1259999999999999</v>
+      </c>
+      <c r="AS101">
+        <v>2.9590000000000001</v>
+      </c>
+      <c r="AT101">
+        <v>-5.8719999999999999</v>
+      </c>
+      <c r="AU101">
+        <v>4.4930000000000003</v>
+      </c>
+      <c r="AV101">
+        <v>-6.5579999999999998</v>
+      </c>
+    </row>
+    <row r="102" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
         <v>2.0166590000000002</v>
       </c>
@@ -5702,8 +7273,41 @@
         <v>24.57273</v>
       </c>
       <c r="AE102" s="1"/>
-    </row>
-    <row r="103" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AJ102">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="AK102">
+        <v>6.0650000000000004</v>
+      </c>
+      <c r="AL102">
+        <v>1.879</v>
+      </c>
+      <c r="AM102">
+        <v>4.3840000000000003</v>
+      </c>
+      <c r="AN102">
+        <v>-7.7130000000000001</v>
+      </c>
+      <c r="AQ102">
+        <v>4.53</v>
+      </c>
+      <c r="AR102">
+        <v>-2.9380000000000002</v>
+      </c>
+      <c r="AS102">
+        <v>2.9689999999999999</v>
+      </c>
+      <c r="AT102">
+        <v>-5.6630000000000003</v>
+      </c>
+      <c r="AU102">
+        <v>4.4960000000000004</v>
+      </c>
+      <c r="AV102">
+        <v>-6.3390000000000004</v>
+      </c>
+    </row>
+    <row r="103" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A103" s="1">
         <v>2.033325</v>
       </c>
@@ -5783,8 +7387,41 @@
         <v>-15.0525</v>
       </c>
       <c r="AI103" s="1"/>
-    </row>
-    <row r="104" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AJ103">
+        <v>2.2170000000000001</v>
+      </c>
+      <c r="AK103">
+        <v>6.0970000000000004</v>
+      </c>
+      <c r="AL103">
+        <v>1.9690000000000001</v>
+      </c>
+      <c r="AM103">
+        <v>4.3860000000000001</v>
+      </c>
+      <c r="AN103">
+        <v>-7.5279999999999996</v>
+      </c>
+      <c r="AQ103">
+        <v>4.5359999999999996</v>
+      </c>
+      <c r="AR103">
+        <v>-2.7490000000000001</v>
+      </c>
+      <c r="AS103">
+        <v>2.9790000000000001</v>
+      </c>
+      <c r="AT103">
+        <v>-5.4429999999999996</v>
+      </c>
+      <c r="AU103">
+        <v>4.4980000000000002</v>
+      </c>
+      <c r="AV103">
+        <v>-6.0780000000000003</v>
+      </c>
+    </row>
+    <row r="104" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A104" s="1">
         <v>2.049992</v>
       </c>
@@ -5865,10 +7502,40 @@
       </c>
       <c r="AI104" s="1"/>
       <c r="AJ104" s="1">
-        <v>25.24907</v>
-      </c>
-    </row>
-    <row r="105" spans="1:36" x14ac:dyDescent="0.3">
+        <v>2.2330000000000001</v>
+      </c>
+      <c r="AK104">
+        <v>6.1280000000000001</v>
+      </c>
+      <c r="AL104">
+        <v>2.0680000000000001</v>
+      </c>
+      <c r="AM104">
+        <v>4.3869999999999996</v>
+      </c>
+      <c r="AN104">
+        <v>-7.343</v>
+      </c>
+      <c r="AQ104">
+        <v>4.5369999999999999</v>
+      </c>
+      <c r="AR104">
+        <v>-2.5430000000000001</v>
+      </c>
+      <c r="AS104">
+        <v>2.9849999999999999</v>
+      </c>
+      <c r="AT104">
+        <v>-5.25</v>
+      </c>
+      <c r="AU104">
+        <v>4.5019999999999998</v>
+      </c>
+      <c r="AV104">
+        <v>-5.8310000000000004</v>
+      </c>
+    </row>
+    <row r="105" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A105" s="1">
         <v>2.0666579999999999</v>
       </c>
@@ -5949,10 +7616,40 @@
       </c>
       <c r="AI105" s="1"/>
       <c r="AJ105" s="1">
-        <v>26.849450000000001</v>
-      </c>
-    </row>
-    <row r="106" spans="1:36" x14ac:dyDescent="0.3">
+        <v>2.25</v>
+      </c>
+      <c r="AK105">
+        <v>6.157</v>
+      </c>
+      <c r="AL105">
+        <v>2.1680000000000001</v>
+      </c>
+      <c r="AM105">
+        <v>4.3860000000000001</v>
+      </c>
+      <c r="AN105">
+        <v>-7.1840000000000002</v>
+      </c>
+      <c r="AQ105">
+        <v>4.54</v>
+      </c>
+      <c r="AR105">
+        <v>-2.3650000000000002</v>
+      </c>
+      <c r="AS105">
+        <v>2.9950000000000001</v>
+      </c>
+      <c r="AT105">
+        <v>-5.0380000000000003</v>
+      </c>
+      <c r="AU105">
+        <v>4.5010000000000003</v>
+      </c>
+      <c r="AV105">
+        <v>-5.61</v>
+      </c>
+    </row>
+    <row r="106" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A106" s="1">
         <v>2.0833249999999999</v>
       </c>
@@ -6033,10 +7730,40 @@
       </c>
       <c r="AI106" s="1"/>
       <c r="AJ106" s="1">
-        <v>26.693239999999999</v>
-      </c>
-    </row>
-    <row r="107" spans="1:36" x14ac:dyDescent="0.3">
+        <v>2.2669999999999999</v>
+      </c>
+      <c r="AK106">
+        <v>6.1820000000000004</v>
+      </c>
+      <c r="AL106">
+        <v>2.2549999999999999</v>
+      </c>
+      <c r="AM106">
+        <v>4.3849999999999998</v>
+      </c>
+      <c r="AN106">
+        <v>-6.9939999999999998</v>
+      </c>
+      <c r="AQ106">
+        <v>4.5439999999999996</v>
+      </c>
+      <c r="AR106">
+        <v>-2.177</v>
+      </c>
+      <c r="AS106">
+        <v>2.9969999999999999</v>
+      </c>
+      <c r="AT106">
+        <v>-4.8239999999999998</v>
+      </c>
+      <c r="AU106">
+        <v>4.508</v>
+      </c>
+      <c r="AV106">
+        <v>-5.3620000000000001</v>
+      </c>
+    </row>
+    <row r="107" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A107" s="1">
         <v>2.0999919999999999</v>
       </c>
@@ -6117,10 +7844,40 @@
       </c>
       <c r="AI107" s="1"/>
       <c r="AJ107" s="1">
-        <v>25.034479999999999</v>
-      </c>
-    </row>
-    <row r="108" spans="1:36" x14ac:dyDescent="0.3">
+        <v>2.2829999999999999</v>
+      </c>
+      <c r="AK107">
+        <v>6.2</v>
+      </c>
+      <c r="AL107">
+        <v>2.3570000000000002</v>
+      </c>
+      <c r="AM107">
+        <v>4.3810000000000002</v>
+      </c>
+      <c r="AN107">
+        <v>-6.806</v>
+      </c>
+      <c r="AQ107">
+        <v>4.5510000000000002</v>
+      </c>
+      <c r="AR107">
+        <v>-1.976</v>
+      </c>
+      <c r="AS107">
+        <v>3.0030000000000001</v>
+      </c>
+      <c r="AT107">
+        <v>-4.633</v>
+      </c>
+      <c r="AU107">
+        <v>4.5229999999999997</v>
+      </c>
+      <c r="AV107">
+        <v>-5.1349999999999998</v>
+      </c>
+    </row>
+    <row r="108" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A108" s="1">
         <v>2.1166580000000002</v>
       </c>
@@ -6201,10 +7958,40 @@
       </c>
       <c r="AI108" s="1"/>
       <c r="AJ108" s="1">
-        <v>26.266490000000001</v>
-      </c>
-    </row>
-    <row r="109" spans="1:36" x14ac:dyDescent="0.3">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="AK108">
+        <v>6.2190000000000003</v>
+      </c>
+      <c r="AL108">
+        <v>2.4460000000000002</v>
+      </c>
+      <c r="AM108">
+        <v>4.38</v>
+      </c>
+      <c r="AN108">
+        <v>-6.6470000000000002</v>
+      </c>
+      <c r="AQ108">
+        <v>4.5599999999999996</v>
+      </c>
+      <c r="AR108">
+        <v>-1.7989999999999999</v>
+      </c>
+      <c r="AS108">
+        <v>3.0070000000000001</v>
+      </c>
+      <c r="AT108">
+        <v>-4.4130000000000003</v>
+      </c>
+      <c r="AU108">
+        <v>4.5309999999999997</v>
+      </c>
+      <c r="AV108">
+        <v>-4.9119999999999999</v>
+      </c>
+    </row>
+    <row r="109" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A109" s="1">
         <v>2.1333250000000001</v>
       </c>
@@ -6285,10 +8072,40 @@
       </c>
       <c r="AI109" s="1"/>
       <c r="AJ109" s="1">
-        <v>25.399480000000001</v>
-      </c>
-    </row>
-    <row r="110" spans="1:36" x14ac:dyDescent="0.3">
+        <v>2.3170000000000002</v>
+      </c>
+      <c r="AK109">
+        <v>6.23</v>
+      </c>
+      <c r="AL109">
+        <v>2.532</v>
+      </c>
+      <c r="AM109">
+        <v>4.3789999999999996</v>
+      </c>
+      <c r="AN109">
+        <v>-6.4660000000000002</v>
+      </c>
+      <c r="AQ109">
+        <v>4.5739999999999998</v>
+      </c>
+      <c r="AR109">
+        <v>-1.6120000000000001</v>
+      </c>
+      <c r="AS109">
+        <v>3.0139999999999998</v>
+      </c>
+      <c r="AT109">
+        <v>-4.2169999999999996</v>
+      </c>
+      <c r="AU109">
+        <v>4.5359999999999996</v>
+      </c>
+      <c r="AV109">
+        <v>-4.6680000000000001</v>
+      </c>
+    </row>
+    <row r="110" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A110" s="1">
         <v>2.149991</v>
       </c>
@@ -6369,10 +8186,40 @@
       </c>
       <c r="AI110" s="1"/>
       <c r="AJ110" s="1">
-        <v>25.226050000000001</v>
-      </c>
-    </row>
-    <row r="111" spans="1:36" x14ac:dyDescent="0.3">
+        <v>2.3330000000000002</v>
+      </c>
+      <c r="AK110">
+        <v>6.2460000000000004</v>
+      </c>
+      <c r="AL110">
+        <v>2.6160000000000001</v>
+      </c>
+      <c r="AM110">
+        <v>4.38</v>
+      </c>
+      <c r="AN110">
+        <v>-6.2889999999999997</v>
+      </c>
+      <c r="AQ110">
+        <v>4.5860000000000003</v>
+      </c>
+      <c r="AR110">
+        <v>-1.4239999999999999</v>
+      </c>
+      <c r="AS110">
+        <v>3.0190000000000001</v>
+      </c>
+      <c r="AT110">
+        <v>-4.032</v>
+      </c>
+      <c r="AU110">
+        <v>4.5389999999999997</v>
+      </c>
+      <c r="AV110">
+        <v>-4.444</v>
+      </c>
+    </row>
+    <row r="111" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A111" s="1">
         <v>2.166658</v>
       </c>
@@ -6453,10 +8300,40 @@
       </c>
       <c r="AI111" s="1"/>
       <c r="AJ111" s="1">
-        <v>26.12866</v>
-      </c>
-    </row>
-    <row r="112" spans="1:36" x14ac:dyDescent="0.3">
+        <v>2.35</v>
+      </c>
+      <c r="AK111">
+        <v>6.2590000000000003</v>
+      </c>
+      <c r="AL111">
+        <v>2.7130000000000001</v>
+      </c>
+      <c r="AM111">
+        <v>4.38</v>
+      </c>
+      <c r="AN111">
+        <v>-6.1230000000000002</v>
+      </c>
+      <c r="AQ111">
+        <v>4.6079999999999997</v>
+      </c>
+      <c r="AR111">
+        <v>-1.254</v>
+      </c>
+      <c r="AS111">
+        <v>3.028</v>
+      </c>
+      <c r="AT111">
+        <v>-3.8170000000000002</v>
+      </c>
+      <c r="AU111">
+        <v>4.5380000000000003</v>
+      </c>
+      <c r="AV111">
+        <v>-4.21</v>
+      </c>
+    </row>
+    <row r="112" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A112" s="1">
         <v>2.183325</v>
       </c>
@@ -6537,10 +8414,40 @@
       </c>
       <c r="AI112" s="1"/>
       <c r="AJ112" s="1">
-        <v>23.775839999999999</v>
-      </c>
-    </row>
-    <row r="113" spans="1:36" x14ac:dyDescent="0.3">
+        <v>2.367</v>
+      </c>
+      <c r="AK112">
+        <v>6.2690000000000001</v>
+      </c>
+      <c r="AL112">
+        <v>2.7930000000000001</v>
+      </c>
+      <c r="AM112">
+        <v>4.3789999999999996</v>
+      </c>
+      <c r="AN112">
+        <v>-5.9420000000000002</v>
+      </c>
+      <c r="AQ112">
+        <v>4.6310000000000002</v>
+      </c>
+      <c r="AR112">
+        <v>-1.071</v>
+      </c>
+      <c r="AS112">
+        <v>3.0310000000000001</v>
+      </c>
+      <c r="AT112">
+        <v>-3.6280000000000001</v>
+      </c>
+      <c r="AU112">
+        <v>4.5369999999999999</v>
+      </c>
+      <c r="AV112">
+        <v>-3.9580000000000002</v>
+      </c>
+    </row>
+    <row r="113" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A113" s="1">
         <v>2.1999909999999998</v>
       </c>
@@ -6621,10 +8528,40 @@
       </c>
       <c r="AI113" s="1"/>
       <c r="AJ113" s="1">
-        <v>24.524940000000001</v>
-      </c>
-    </row>
-    <row r="114" spans="1:36" x14ac:dyDescent="0.3">
+        <v>2.383</v>
+      </c>
+      <c r="AK113">
+        <v>6.2880000000000003</v>
+      </c>
+      <c r="AL113">
+        <v>2.8820000000000001</v>
+      </c>
+      <c r="AM113">
+        <v>4.3760000000000003</v>
+      </c>
+      <c r="AN113">
+        <v>-5.7709999999999999</v>
+      </c>
+      <c r="AQ113">
+        <v>4.66</v>
+      </c>
+      <c r="AR113">
+        <v>-0.88600000000000001</v>
+      </c>
+      <c r="AS113">
+        <v>3.044</v>
+      </c>
+      <c r="AT113">
+        <v>-3.4489999999999998</v>
+      </c>
+      <c r="AU113">
+        <v>4.5359999999999996</v>
+      </c>
+      <c r="AV113">
+        <v>-3.7349999999999999</v>
+      </c>
+    </row>
+    <row r="114" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A114" s="1">
         <v>2.2166579999999998</v>
       </c>
@@ -6705,10 +8642,40 @@
       </c>
       <c r="AI114" s="1"/>
       <c r="AJ114" s="1">
-        <v>25.97307</v>
-      </c>
-    </row>
-    <row r="115" spans="1:36" x14ac:dyDescent="0.3">
+        <v>2.4</v>
+      </c>
+      <c r="AK114">
+        <v>6.32</v>
+      </c>
+      <c r="AL114">
+        <v>2.984</v>
+      </c>
+      <c r="AM114">
+        <v>4.3769999999999998</v>
+      </c>
+      <c r="AN114">
+        <v>-5.6139999999999999</v>
+      </c>
+      <c r="AQ114">
+        <v>4.6840000000000002</v>
+      </c>
+      <c r="AR114">
+        <v>-0.72699999999999998</v>
+      </c>
+      <c r="AS114">
+        <v>3.0569999999999999</v>
+      </c>
+      <c r="AT114">
+        <v>-3.2480000000000002</v>
+      </c>
+      <c r="AU114">
+        <v>4.5339999999999998</v>
+      </c>
+      <c r="AV114">
+        <v>-3.5049999999999999</v>
+      </c>
+    </row>
+    <row r="115" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A115" s="1">
         <v>2.2333240000000001</v>
       </c>
@@ -6789,10 +8756,40 @@
       </c>
       <c r="AI115" s="1"/>
       <c r="AJ115" s="1">
-        <v>23.96987</v>
-      </c>
-    </row>
-    <row r="116" spans="1:36" x14ac:dyDescent="0.3">
+        <v>2.4169999999999998</v>
+      </c>
+      <c r="AK115">
+        <v>6.3479999999999999</v>
+      </c>
+      <c r="AL115">
+        <v>3.0750000000000002</v>
+      </c>
+      <c r="AM115">
+        <v>4.3849999999999998</v>
+      </c>
+      <c r="AN115">
+        <v>-5.4530000000000003</v>
+      </c>
+      <c r="AQ115">
+        <v>4.7190000000000003</v>
+      </c>
+      <c r="AR115">
+        <v>-0.54300000000000004</v>
+      </c>
+      <c r="AS115">
+        <v>3.0670000000000002</v>
+      </c>
+      <c r="AT115">
+        <v>-3.069</v>
+      </c>
+      <c r="AU115">
+        <v>4.53</v>
+      </c>
+      <c r="AV115">
+        <v>-3.254</v>
+      </c>
+    </row>
+    <row r="116" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A116" s="1">
         <v>2.2499910000000001</v>
       </c>
@@ -6873,10 +8870,40 @@
       </c>
       <c r="AI116" s="1"/>
       <c r="AJ116" s="1">
-        <v>24.03313</v>
-      </c>
-    </row>
-    <row r="117" spans="1:36" x14ac:dyDescent="0.3">
+        <v>2.4329999999999998</v>
+      </c>
+      <c r="AK116">
+        <v>6.3810000000000002</v>
+      </c>
+      <c r="AL116">
+        <v>3.1819999999999999</v>
+      </c>
+      <c r="AM116">
+        <v>4.4009999999999998</v>
+      </c>
+      <c r="AN116">
+        <v>-5.31</v>
+      </c>
+      <c r="AQ116">
+        <v>4.75</v>
+      </c>
+      <c r="AR116">
+        <v>-0.36499999999999999</v>
+      </c>
+      <c r="AS116">
+        <v>3.0819999999999999</v>
+      </c>
+      <c r="AT116">
+        <v>-2.891</v>
+      </c>
+      <c r="AU116">
+        <v>4.53</v>
+      </c>
+      <c r="AV116">
+        <v>-3.0369999999999999</v>
+      </c>
+    </row>
+    <row r="117" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A117" s="1">
         <v>2.2666580000000001</v>
       </c>
@@ -6957,10 +8984,40 @@
       </c>
       <c r="AI117" s="1"/>
       <c r="AJ117" s="1">
-        <v>24.31812</v>
-      </c>
-    </row>
-    <row r="118" spans="1:36" x14ac:dyDescent="0.3">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="AK117">
+        <v>6.4139999999999997</v>
+      </c>
+      <c r="AL117">
+        <v>3.2850000000000001</v>
+      </c>
+      <c r="AM117">
+        <v>4.4160000000000004</v>
+      </c>
+      <c r="AN117">
+        <v>-5.1719999999999997</v>
+      </c>
+      <c r="AQ117">
+        <v>4.7830000000000004</v>
+      </c>
+      <c r="AR117">
+        <v>-0.20100000000000001</v>
+      </c>
+      <c r="AS117">
+        <v>3.0979999999999999</v>
+      </c>
+      <c r="AT117">
+        <v>-2.6909999999999998</v>
+      </c>
+      <c r="AU117">
+        <v>4.5250000000000004</v>
+      </c>
+      <c r="AV117">
+        <v>-2.8029999999999999</v>
+      </c>
+    </row>
+    <row r="118" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A118" s="1">
         <v>2.2833239999999999</v>
       </c>
@@ -7041,10 +9098,40 @@
       </c>
       <c r="AI118" s="1"/>
       <c r="AJ118" s="1">
-        <v>23.028970000000001</v>
-      </c>
-    </row>
-    <row r="119" spans="1:36" x14ac:dyDescent="0.3">
+        <v>2.4670000000000001</v>
+      </c>
+      <c r="AK118">
+        <v>6.44</v>
+      </c>
+      <c r="AL118">
+        <v>3.3780000000000001</v>
+      </c>
+      <c r="AM118">
+        <v>4.4279999999999999</v>
+      </c>
+      <c r="AN118">
+        <v>-5.01</v>
+      </c>
+      <c r="AQ118">
+        <v>4.8369999999999997</v>
+      </c>
+      <c r="AR118" s="1">
+        <v>-9.0629999999999999E-3</v>
+      </c>
+      <c r="AS118">
+        <v>3.1160000000000001</v>
+      </c>
+      <c r="AT118">
+        <v>-2.5150000000000001</v>
+      </c>
+      <c r="AU118">
+        <v>4.5259999999999998</v>
+      </c>
+      <c r="AV118">
+        <v>-2.5630000000000002</v>
+      </c>
+    </row>
+    <row r="119" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A119" s="1">
         <v>2.2999909999999999</v>
       </c>
@@ -7125,10 +9212,40 @@
       </c>
       <c r="AI119" s="1"/>
       <c r="AJ119" s="1">
-        <v>23.9206</v>
-      </c>
-    </row>
-    <row r="120" spans="1:36" x14ac:dyDescent="0.3">
+        <v>2.4830000000000001</v>
+      </c>
+      <c r="AK119">
+        <v>6.468</v>
+      </c>
+      <c r="AL119">
+        <v>3.4790000000000001</v>
+      </c>
+      <c r="AM119">
+        <v>4.4390000000000001</v>
+      </c>
+      <c r="AN119">
+        <v>-4.8630000000000004</v>
+      </c>
+      <c r="AQ119">
+        <v>4.8780000000000001</v>
+      </c>
+      <c r="AR119">
+        <v>0.16200000000000001</v>
+      </c>
+      <c r="AS119">
+        <v>3.1379999999999999</v>
+      </c>
+      <c r="AT119">
+        <v>-2.34</v>
+      </c>
+      <c r="AU119">
+        <v>4.5289999999999999</v>
+      </c>
+      <c r="AV119">
+        <v>-2.351</v>
+      </c>
+    </row>
+    <row r="120" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A120" s="1">
         <v>2.3166570000000002</v>
       </c>
@@ -7209,10 +9326,40 @@
       </c>
       <c r="AI120" s="1"/>
       <c r="AJ120" s="1">
-        <v>23.985189999999999</v>
-      </c>
-    </row>
-    <row r="121" spans="1:36" x14ac:dyDescent="0.3">
+        <v>2.5</v>
+      </c>
+      <c r="AK120">
+        <v>6.4980000000000002</v>
+      </c>
+      <c r="AL120">
+        <v>3.5819999999999999</v>
+      </c>
+      <c r="AM120">
+        <v>4.4459999999999997</v>
+      </c>
+      <c r="AN120">
+        <v>-4.7160000000000002</v>
+      </c>
+      <c r="AQ120">
+        <v>4.9169999999999998</v>
+      </c>
+      <c r="AR120">
+        <v>0.32400000000000001</v>
+      </c>
+      <c r="AS120">
+        <v>3.1579999999999999</v>
+      </c>
+      <c r="AT120">
+        <v>-2.157</v>
+      </c>
+      <c r="AU120">
+        <v>4.5289999999999999</v>
+      </c>
+      <c r="AV120">
+        <v>-2.1040000000000001</v>
+      </c>
+    </row>
+    <row r="121" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A121" s="1">
         <v>2.3333240000000002</v>
       </c>
@@ -7293,10 +9440,40 @@
       </c>
       <c r="AI121" s="1"/>
       <c r="AJ121" s="1">
-        <v>23.438189999999999</v>
-      </c>
-    </row>
-    <row r="122" spans="1:36" x14ac:dyDescent="0.3">
+        <v>2.5169999999999999</v>
+      </c>
+      <c r="AK121">
+        <v>6.5279999999999996</v>
+      </c>
+      <c r="AL121">
+        <v>3.673</v>
+      </c>
+      <c r="AM121">
+        <v>4.45</v>
+      </c>
+      <c r="AN121">
+        <v>-4.55</v>
+      </c>
+      <c r="AQ121">
+        <v>4.9749999999999996</v>
+      </c>
+      <c r="AR121">
+        <v>0.51300000000000001</v>
+      </c>
+      <c r="AS121">
+        <v>3.181</v>
+      </c>
+      <c r="AT121">
+        <v>-1.9910000000000001</v>
+      </c>
+      <c r="AU121">
+        <v>4.5339999999999998</v>
+      </c>
+      <c r="AV121">
+        <v>-1.8779999999999999</v>
+      </c>
+    </row>
+    <row r="122" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A122" s="1">
         <v>2.3499910000000002</v>
       </c>
@@ -7377,10 +9554,40 @@
       </c>
       <c r="AI122" s="1"/>
       <c r="AJ122" s="1">
-        <v>24.868110000000001</v>
-      </c>
-    </row>
-    <row r="123" spans="1:36" x14ac:dyDescent="0.3">
+        <v>2.5329999999999999</v>
+      </c>
+      <c r="AK122">
+        <v>6.5579999999999998</v>
+      </c>
+      <c r="AL122">
+        <v>3.7690000000000001</v>
+      </c>
+      <c r="AM122">
+        <v>4.452</v>
+      </c>
+      <c r="AN122">
+        <v>-4.4050000000000002</v>
+      </c>
+      <c r="AQ122">
+        <v>5.0179999999999998</v>
+      </c>
+      <c r="AR122">
+        <v>0.68400000000000005</v>
+      </c>
+      <c r="AS122">
+        <v>3.2130000000000001</v>
+      </c>
+      <c r="AT122">
+        <v>-1.821</v>
+      </c>
+      <c r="AU122">
+        <v>4.5410000000000004</v>
+      </c>
+      <c r="AV122">
+        <v>-1.67</v>
+      </c>
+    </row>
+    <row r="123" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A123" s="1">
         <v>2.366657</v>
       </c>
@@ -7461,10 +9668,40 @@
       </c>
       <c r="AI123" s="1"/>
       <c r="AJ123" s="1">
-        <v>24.318989999999999</v>
-      </c>
-    </row>
-    <row r="124" spans="1:36" x14ac:dyDescent="0.3">
+        <v>2.5499999999999998</v>
+      </c>
+      <c r="AK123">
+        <v>6.5890000000000004</v>
+      </c>
+      <c r="AL123">
+        <v>3.8650000000000002</v>
+      </c>
+      <c r="AM123">
+        <v>4.4530000000000003</v>
+      </c>
+      <c r="AN123">
+        <v>-4.2549999999999999</v>
+      </c>
+      <c r="AQ123">
+        <v>5.0679999999999996</v>
+      </c>
+      <c r="AR123">
+        <v>0.84799999999999998</v>
+      </c>
+      <c r="AS123">
+        <v>3.2570000000000001</v>
+      </c>
+      <c r="AT123">
+        <v>-1.65</v>
+      </c>
+      <c r="AU123">
+        <v>4.5469999999999997</v>
+      </c>
+      <c r="AV123">
+        <v>-1.429</v>
+      </c>
+    </row>
+    <row r="124" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A124" s="1">
         <v>2.383324</v>
       </c>
@@ -7545,10 +9782,40 @@
       </c>
       <c r="AI124" s="1"/>
       <c r="AJ124" s="1">
-        <v>23.149349999999998</v>
-      </c>
-    </row>
-    <row r="125" spans="1:36" x14ac:dyDescent="0.3">
+        <v>2.5670000000000002</v>
+      </c>
+      <c r="AK124">
+        <v>6.6130000000000004</v>
+      </c>
+      <c r="AL124">
+        <v>3.96</v>
+      </c>
+      <c r="AM124">
+        <v>4.4539999999999997</v>
+      </c>
+      <c r="AN124">
+        <v>-4.085</v>
+      </c>
+      <c r="AQ124">
+        <v>5.1219999999999999</v>
+      </c>
+      <c r="AR124">
+        <v>1.0369999999999999</v>
+      </c>
+      <c r="AS124">
+        <v>3.3029999999999999</v>
+      </c>
+      <c r="AT124">
+        <v>-1.512</v>
+      </c>
+      <c r="AU124">
+        <v>4.5650000000000004</v>
+      </c>
+      <c r="AV124">
+        <v>-1.208</v>
+      </c>
+    </row>
+    <row r="125" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A125" s="1">
         <v>2.3999899999999998</v>
       </c>
@@ -7629,10 +9896,40 @@
       </c>
       <c r="AI125" s="1"/>
       <c r="AJ125" s="1">
-        <v>24.629580000000001</v>
-      </c>
-    </row>
-    <row r="126" spans="1:36" x14ac:dyDescent="0.3">
+        <v>2.5830000000000002</v>
+      </c>
+      <c r="AK125">
+        <v>6.6360000000000001</v>
+      </c>
+      <c r="AL125">
+        <v>4.0579999999999998</v>
+      </c>
+      <c r="AM125">
+        <v>4.452</v>
+      </c>
+      <c r="AN125">
+        <v>-3.9390000000000001</v>
+      </c>
+      <c r="AQ125">
+        <v>5.1719999999999997</v>
+      </c>
+      <c r="AR125">
+        <v>1.206</v>
+      </c>
+      <c r="AS125">
+        <v>3.3639999999999999</v>
+      </c>
+      <c r="AT125">
+        <v>-1.361</v>
+      </c>
+      <c r="AU125">
+        <v>4.5780000000000003</v>
+      </c>
+      <c r="AV125">
+        <v>-0.999</v>
+      </c>
+    </row>
+    <row r="126" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A126" s="1">
         <v>2.4166569999999998</v>
       </c>
@@ -7713,10 +10010,40 @@
       </c>
       <c r="AI126" s="1"/>
       <c r="AJ126" s="1">
-        <v>23.954319999999999</v>
-      </c>
-    </row>
-    <row r="127" spans="1:36" x14ac:dyDescent="0.3">
+        <v>2.6</v>
+      </c>
+      <c r="AK126">
+        <v>6.6630000000000003</v>
+      </c>
+      <c r="AL126">
+        <v>4.1559999999999997</v>
+      </c>
+      <c r="AM126">
+        <v>4.4509999999999996</v>
+      </c>
+      <c r="AN126">
+        <v>-3.7829999999999999</v>
+      </c>
+      <c r="AQ126">
+        <v>5.2160000000000002</v>
+      </c>
+      <c r="AR126">
+        <v>1.373</v>
+      </c>
+      <c r="AS126">
+        <v>3.4409999999999998</v>
+      </c>
+      <c r="AT126">
+        <v>-1.208</v>
+      </c>
+      <c r="AU126">
+        <v>4.601</v>
+      </c>
+      <c r="AV126">
+        <v>-0.77300000000000002</v>
+      </c>
+    </row>
+    <row r="127" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A127" s="1">
         <v>2.4333239999999998</v>
       </c>
@@ -7797,10 +10124,40 @@
       </c>
       <c r="AI127" s="1"/>
       <c r="AJ127" s="1">
-        <v>23.07048</v>
-      </c>
-    </row>
-    <row r="128" spans="1:36" x14ac:dyDescent="0.3">
+        <v>2.617</v>
+      </c>
+      <c r="AK127">
+        <v>6.6909999999999998</v>
+      </c>
+      <c r="AL127">
+        <v>4.2430000000000003</v>
+      </c>
+      <c r="AM127">
+        <v>4.4459999999999997</v>
+      </c>
+      <c r="AN127">
+        <v>-3.6190000000000002</v>
+      </c>
+      <c r="AQ127">
+        <v>5.2729999999999997</v>
+      </c>
+      <c r="AR127">
+        <v>1.5580000000000001</v>
+      </c>
+      <c r="AS127">
+        <v>3.5179999999999998</v>
+      </c>
+      <c r="AT127">
+        <v>-1.0720000000000001</v>
+      </c>
+      <c r="AU127">
+        <v>4.617</v>
+      </c>
+      <c r="AV127">
+        <v>-0.55600000000000005</v>
+      </c>
+    </row>
+    <row r="128" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A128" s="1">
         <v>2.4499900000000001</v>
       </c>
@@ -7881,10 +10238,40 @@
       </c>
       <c r="AI128" s="1"/>
       <c r="AJ128" s="1">
-        <v>24.259509999999999</v>
-      </c>
-    </row>
-    <row r="129" spans="1:36" x14ac:dyDescent="0.3">
+        <v>2.633</v>
+      </c>
+      <c r="AK128">
+        <v>6.718</v>
+      </c>
+      <c r="AL128">
+        <v>4.3410000000000002</v>
+      </c>
+      <c r="AM128">
+        <v>4.4429999999999996</v>
+      </c>
+      <c r="AN128">
+        <v>-3.4740000000000002</v>
+      </c>
+      <c r="AQ128">
+        <v>5.3159999999999998</v>
+      </c>
+      <c r="AR128">
+        <v>1.7210000000000001</v>
+      </c>
+      <c r="AS128">
+        <v>3.6150000000000002</v>
+      </c>
+      <c r="AT128">
+        <v>-0.92200000000000004</v>
+      </c>
+      <c r="AU128">
+        <v>4.6429999999999998</v>
+      </c>
+      <c r="AV128">
+        <v>-0.35199999999999998</v>
+      </c>
+    </row>
+    <row r="129" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A129" s="1">
         <v>2.4666570000000001</v>
       </c>
@@ -7965,10 +10352,40 @@
       </c>
       <c r="AI129" s="1"/>
       <c r="AJ129" s="1">
-        <v>23.143599999999999</v>
-      </c>
-    </row>
-    <row r="130" spans="1:36" x14ac:dyDescent="0.3">
+        <v>2.65</v>
+      </c>
+      <c r="AK129">
+        <v>6.7359999999999998</v>
+      </c>
+      <c r="AL129">
+        <v>4.4340000000000002</v>
+      </c>
+      <c r="AM129">
+        <v>4.4370000000000003</v>
+      </c>
+      <c r="AN129">
+        <v>-3.3079999999999998</v>
+      </c>
+      <c r="AQ129">
+        <v>5.367</v>
+      </c>
+      <c r="AR129">
+        <v>1.8859999999999999</v>
+      </c>
+      <c r="AS129">
+        <v>3.7210000000000001</v>
+      </c>
+      <c r="AT129">
+        <v>-0.78800000000000003</v>
+      </c>
+      <c r="AU129">
+        <v>4.673</v>
+      </c>
+      <c r="AV129">
+        <v>-0.123</v>
+      </c>
+    </row>
+    <row r="130" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A130" s="1">
         <v>2.4833229999999999</v>
       </c>
@@ -8049,10 +10466,40 @@
       </c>
       <c r="AI130" s="1"/>
       <c r="AJ130" s="1">
-        <v>23.483750000000001</v>
-      </c>
-    </row>
-    <row r="131" spans="1:36" x14ac:dyDescent="0.3">
+        <v>2.6669999999999998</v>
+      </c>
+      <c r="AK130">
+        <v>6.7640000000000002</v>
+      </c>
+      <c r="AL130">
+        <v>4.5170000000000003</v>
+      </c>
+      <c r="AM130">
+        <v>4.4290000000000003</v>
+      </c>
+      <c r="AN130">
+        <v>-3.141</v>
+      </c>
+      <c r="AQ130">
+        <v>5.4160000000000004</v>
+      </c>
+      <c r="AR130">
+        <v>2.0670000000000002</v>
+      </c>
+      <c r="AS130">
+        <v>3.8239999999999998</v>
+      </c>
+      <c r="AT130">
+        <v>-0.66500000000000004</v>
+      </c>
+      <c r="AU130">
+        <v>4.702</v>
+      </c>
+      <c r="AV130" s="1">
+        <v>8.3280000000000007E-2</v>
+      </c>
+    </row>
+    <row r="131" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A131" s="1">
         <v>2.4999899999999999</v>
       </c>
@@ -8133,10 +10580,40 @@
       </c>
       <c r="AI131" s="1"/>
       <c r="AJ131" s="1">
-        <v>24.197870000000002</v>
-      </c>
-    </row>
-    <row r="132" spans="1:36" x14ac:dyDescent="0.3">
+        <v>2.6829999999999998</v>
+      </c>
+      <c r="AK131">
+        <v>6.7880000000000003</v>
+      </c>
+      <c r="AL131">
+        <v>4.62</v>
+      </c>
+      <c r="AM131">
+        <v>4.4249999999999998</v>
+      </c>
+      <c r="AN131">
+        <v>-2.9990000000000001</v>
+      </c>
+      <c r="AQ131">
+        <v>5.4530000000000003</v>
+      </c>
+      <c r="AR131">
+        <v>2.2200000000000002</v>
+      </c>
+      <c r="AS131">
+        <v>3.94</v>
+      </c>
+      <c r="AT131">
+        <v>-0.52500000000000002</v>
+      </c>
+      <c r="AU131">
+        <v>4.74</v>
+      </c>
+      <c r="AV131">
+        <v>0.29199999999999998</v>
+      </c>
+    </row>
+    <row r="132" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A132" s="1">
         <v>2.5166569999999999</v>
       </c>
@@ -8217,10 +10694,40 @@
       </c>
       <c r="AI132" s="1"/>
       <c r="AJ132" s="1">
-        <v>22.206440000000001</v>
-      </c>
-    </row>
-    <row r="133" spans="1:36" x14ac:dyDescent="0.3">
+        <v>2.7</v>
+      </c>
+      <c r="AK132">
+        <v>6.8120000000000003</v>
+      </c>
+      <c r="AL132">
+        <v>4.7069999999999999</v>
+      </c>
+      <c r="AM132">
+        <v>4.42</v>
+      </c>
+      <c r="AN132">
+        <v>-2.84</v>
+      </c>
+      <c r="AQ132">
+        <v>5.4980000000000002</v>
+      </c>
+      <c r="AR132">
+        <v>2.387</v>
+      </c>
+      <c r="AS132">
+        <v>4.0579999999999998</v>
+      </c>
+      <c r="AT132">
+        <v>-0.39</v>
+      </c>
+      <c r="AU132">
+        <v>4.7830000000000004</v>
+      </c>
+      <c r="AV132">
+        <v>0.51900000000000002</v>
+      </c>
+    </row>
+    <row r="133" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A133" s="1">
         <v>2.5333230000000002</v>
       </c>
@@ -8301,10 +10808,40 @@
       </c>
       <c r="AI133" s="1"/>
       <c r="AJ133" s="1">
-        <v>22.98001</v>
-      </c>
-    </row>
-    <row r="134" spans="1:36" x14ac:dyDescent="0.3">
+        <v>2.7170000000000001</v>
+      </c>
+      <c r="AK133">
+        <v>6.8339999999999996</v>
+      </c>
+      <c r="AL133">
+        <v>4.8</v>
+      </c>
+      <c r="AM133">
+        <v>4.42</v>
+      </c>
+      <c r="AN133">
+        <v>-2.6779999999999999</v>
+      </c>
+      <c r="AQ133">
+        <v>5.5430000000000001</v>
+      </c>
+      <c r="AR133">
+        <v>2.5649999999999999</v>
+      </c>
+      <c r="AS133">
+        <v>4.1660000000000004</v>
+      </c>
+      <c r="AT133">
+        <v>-0.26100000000000001</v>
+      </c>
+      <c r="AU133">
+        <v>4.8150000000000004</v>
+      </c>
+      <c r="AV133">
+        <v>0.71899999999999997</v>
+      </c>
+    </row>
+    <row r="134" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A134" s="1">
         <v>2.5499900000000002</v>
       </c>
@@ -8385,10 +10922,40 @@
       </c>
       <c r="AI134" s="1"/>
       <c r="AJ134" s="1">
-        <v>23.695969999999999</v>
-      </c>
-    </row>
-    <row r="135" spans="1:36" x14ac:dyDescent="0.3">
+        <v>2.7330000000000001</v>
+      </c>
+      <c r="AK134">
+        <v>6.8579999999999997</v>
+      </c>
+      <c r="AL134">
+        <v>4.8949999999999996</v>
+      </c>
+      <c r="AM134">
+        <v>4.4219999999999997</v>
+      </c>
+      <c r="AN134">
+        <v>-2.54</v>
+      </c>
+      <c r="AQ134">
+        <v>5.5780000000000003</v>
+      </c>
+      <c r="AR134">
+        <v>2.718</v>
+      </c>
+      <c r="AS134">
+        <v>4.2910000000000004</v>
+      </c>
+      <c r="AT134">
+        <v>-0.121</v>
+      </c>
+      <c r="AU134">
+        <v>4.8639999999999999</v>
+      </c>
+      <c r="AV134">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="135" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A135" s="1">
         <v>2.566656</v>
       </c>
@@ -8469,10 +11036,40 @@
       </c>
       <c r="AI135" s="1"/>
       <c r="AJ135" s="1">
-        <v>22.06587</v>
-      </c>
-    </row>
-    <row r="136" spans="1:36" x14ac:dyDescent="0.3">
+        <v>2.75</v>
+      </c>
+      <c r="AK135">
+        <v>6.8840000000000003</v>
+      </c>
+      <c r="AL135">
+        <v>4.9820000000000002</v>
+      </c>
+      <c r="AM135">
+        <v>4.423</v>
+      </c>
+      <c r="AN135">
+        <v>-2.3769999999999998</v>
+      </c>
+      <c r="AQ135">
+        <v>5.6150000000000002</v>
+      </c>
+      <c r="AR135">
+        <v>2.8809999999999998</v>
+      </c>
+      <c r="AS135">
+        <v>4.4130000000000003</v>
+      </c>
+      <c r="AT135" s="1">
+        <v>1.052E-2</v>
+      </c>
+      <c r="AU135">
+        <v>4.9089999999999998</v>
+      </c>
+      <c r="AV135">
+        <v>1.1579999999999999</v>
+      </c>
+    </row>
+    <row r="136" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A136" s="1">
         <v>2.583323</v>
       </c>
@@ -8553,10 +11150,40 @@
       </c>
       <c r="AI136" s="1"/>
       <c r="AJ136" s="1">
-        <v>22.318860000000001</v>
-      </c>
-    </row>
-    <row r="137" spans="1:36" x14ac:dyDescent="0.3">
+        <v>2.7669999999999999</v>
+      </c>
+      <c r="AK136">
+        <v>6.9029999999999996</v>
+      </c>
+      <c r="AL136">
+        <v>5.0720000000000001</v>
+      </c>
+      <c r="AM136">
+        <v>4.4219999999999997</v>
+      </c>
+      <c r="AN136">
+        <v>-2.2200000000000002</v>
+      </c>
+      <c r="AQ136">
+        <v>5.6470000000000002</v>
+      </c>
+      <c r="AR136">
+        <v>3.0510000000000002</v>
+      </c>
+      <c r="AS136">
+        <v>4.5270000000000001</v>
+      </c>
+      <c r="AT136">
+        <v>0.13200000000000001</v>
+      </c>
+      <c r="AU136">
+        <v>4.9480000000000004</v>
+      </c>
+      <c r="AV136">
+        <v>1.357</v>
+      </c>
+    </row>
+    <row r="137" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A137" s="1">
         <v>2.59999</v>
       </c>
@@ -8637,10 +11264,40 @@
       </c>
       <c r="AI137" s="1"/>
       <c r="AJ137" s="1">
-        <v>22.743780000000001</v>
-      </c>
-    </row>
-    <row r="138" spans="1:36" x14ac:dyDescent="0.3">
+        <v>2.7829999999999999</v>
+      </c>
+      <c r="AK137">
+        <v>6.9279999999999999</v>
+      </c>
+      <c r="AL137">
+        <v>5.1680000000000001</v>
+      </c>
+      <c r="AM137">
+        <v>4.4269999999999996</v>
+      </c>
+      <c r="AN137">
+        <v>-2.0830000000000002</v>
+      </c>
+      <c r="AQ137">
+        <v>5.6760000000000002</v>
+      </c>
+      <c r="AR137">
+        <v>3.1930000000000001</v>
+      </c>
+      <c r="AS137">
+        <v>4.6609999999999996</v>
+      </c>
+      <c r="AT137">
+        <v>0.27100000000000002</v>
+      </c>
+      <c r="AU137">
+        <v>4.9989999999999997</v>
+      </c>
+      <c r="AV137">
+        <v>1.5760000000000001</v>
+      </c>
+    </row>
+    <row r="138" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A138" s="1">
         <v>2.6166559999999999</v>
       </c>
@@ -8721,10 +11378,40 @@
       </c>
       <c r="AI138" s="1"/>
       <c r="AJ138" s="1">
-        <v>21.679259999999999</v>
-      </c>
-    </row>
-    <row r="139" spans="1:36" x14ac:dyDescent="0.3">
+        <v>2.8</v>
+      </c>
+      <c r="AK138">
+        <v>6.952</v>
+      </c>
+      <c r="AL138">
+        <v>5.25</v>
+      </c>
+      <c r="AM138">
+        <v>4.4349999999999996</v>
+      </c>
+      <c r="AN138">
+        <v>-1.9239999999999999</v>
+      </c>
+      <c r="AQ138">
+        <v>5.7050000000000001</v>
+      </c>
+      <c r="AR138">
+        <v>3.355</v>
+      </c>
+      <c r="AS138">
+        <v>4.7939999999999996</v>
+      </c>
+      <c r="AT138">
+        <v>0.41199999999999998</v>
+      </c>
+      <c r="AU138">
+        <v>5.0469999999999997</v>
+      </c>
+      <c r="AV138">
+        <v>1.798</v>
+      </c>
+    </row>
+    <row r="139" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A139" s="1">
         <v>2.6333229999999999</v>
       </c>
@@ -8805,10 +11492,40 @@
       </c>
       <c r="AI139" s="1"/>
       <c r="AJ139" s="1">
-        <v>22.363230000000001</v>
-      </c>
-    </row>
-    <row r="140" spans="1:36" x14ac:dyDescent="0.3">
+        <v>2.8170000000000002</v>
+      </c>
+      <c r="AK139">
+        <v>6.9720000000000004</v>
+      </c>
+      <c r="AL139">
+        <v>5.3419999999999996</v>
+      </c>
+      <c r="AM139">
+        <v>4.4420000000000002</v>
+      </c>
+      <c r="AN139">
+        <v>-1.776</v>
+      </c>
+      <c r="AQ139">
+        <v>5.7279999999999998</v>
+      </c>
+      <c r="AR139">
+        <v>3.5129999999999999</v>
+      </c>
+      <c r="AS139">
+        <v>4.9089999999999998</v>
+      </c>
+      <c r="AT139">
+        <v>0.52700000000000002</v>
+      </c>
+      <c r="AU139">
+        <v>5.085</v>
+      </c>
+      <c r="AV139">
+        <v>1.992</v>
+      </c>
+    </row>
+    <row r="140" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A140" s="1">
         <v>2.6499890000000001</v>
       </c>
@@ -8889,10 +11606,40 @@
       </c>
       <c r="AI140" s="1"/>
       <c r="AJ140" s="1">
-        <v>22.47015</v>
-      </c>
-    </row>
-    <row r="141" spans="1:36" x14ac:dyDescent="0.3">
+        <v>2.8330000000000002</v>
+      </c>
+      <c r="AK140">
+        <v>6.9980000000000002</v>
+      </c>
+      <c r="AL140">
+        <v>5.4320000000000004</v>
+      </c>
+      <c r="AM140">
+        <v>4.4530000000000003</v>
+      </c>
+      <c r="AN140">
+        <v>-1.6439999999999999</v>
+      </c>
+      <c r="AQ140">
+        <v>5.7569999999999997</v>
+      </c>
+      <c r="AR140">
+        <v>3.6509999999999998</v>
+      </c>
+      <c r="AS140">
+        <v>5.0490000000000004</v>
+      </c>
+      <c r="AT140">
+        <v>0.65900000000000003</v>
+      </c>
+      <c r="AU140">
+        <v>5.1379999999999999</v>
+      </c>
+      <c r="AV140">
+        <v>2.214</v>
+      </c>
+    </row>
+    <row r="141" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A141" s="1">
         <v>2.6666560000000001</v>
       </c>
@@ -8973,10 +11720,40 @@
       </c>
       <c r="AI141" s="1"/>
       <c r="AJ141" s="1">
-        <v>21.5002</v>
-      </c>
-    </row>
-    <row r="142" spans="1:36" x14ac:dyDescent="0.3">
+        <v>2.85</v>
+      </c>
+      <c r="AK141">
+        <v>7.0140000000000002</v>
+      </c>
+      <c r="AL141">
+        <v>5.5229999999999997</v>
+      </c>
+      <c r="AM141">
+        <v>4.4720000000000004</v>
+      </c>
+      <c r="AN141">
+        <v>-1.4930000000000001</v>
+      </c>
+      <c r="AQ141">
+        <v>5.7910000000000004</v>
+      </c>
+      <c r="AR141">
+        <v>3.8170000000000002</v>
+      </c>
+      <c r="AS141">
+        <v>5.1790000000000003</v>
+      </c>
+      <c r="AT141">
+        <v>0.79300000000000004</v>
+      </c>
+      <c r="AU141">
+        <v>5.1790000000000003</v>
+      </c>
+      <c r="AV141">
+        <v>2.4279999999999999</v>
+      </c>
+    </row>
+    <row r="142" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A142" s="1">
         <v>2.6833230000000001</v>
       </c>
@@ -9057,10 +11834,40 @@
       </c>
       <c r="AI142" s="1"/>
       <c r="AJ142" s="1">
-        <v>22.687629999999999</v>
-      </c>
-    </row>
-    <row r="143" spans="1:36" x14ac:dyDescent="0.3">
+        <v>2.867</v>
+      </c>
+      <c r="AK142">
+        <v>7.0350000000000001</v>
+      </c>
+      <c r="AL142">
+        <v>5.6079999999999997</v>
+      </c>
+      <c r="AM142">
+        <v>4.4909999999999997</v>
+      </c>
+      <c r="AN142">
+        <v>-1.345</v>
+      </c>
+      <c r="AQ142">
+        <v>5.8209999999999997</v>
+      </c>
+      <c r="AR142">
+        <v>3.9780000000000002</v>
+      </c>
+      <c r="AS142">
+        <v>5.3029999999999999</v>
+      </c>
+      <c r="AT142">
+        <v>0.92400000000000004</v>
+      </c>
+      <c r="AU142">
+        <v>5.218</v>
+      </c>
+      <c r="AV142">
+        <v>2.6219999999999999</v>
+      </c>
+    </row>
+    <row r="143" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A143" s="1">
         <v>2.699989</v>
       </c>
@@ -9141,10 +11948,40 @@
       </c>
       <c r="AI143" s="1"/>
       <c r="AJ143" s="1">
-        <v>22.171690000000002</v>
-      </c>
-    </row>
-    <row r="144" spans="1:36" x14ac:dyDescent="0.3">
+        <v>2.883</v>
+      </c>
+      <c r="AK143">
+        <v>7.0579999999999998</v>
+      </c>
+      <c r="AL143">
+        <v>5.6920000000000002</v>
+      </c>
+      <c r="AM143">
+        <v>4.5110000000000001</v>
+      </c>
+      <c r="AN143">
+        <v>-1.216</v>
+      </c>
+      <c r="AQ143">
+        <v>5.8540000000000001</v>
+      </c>
+      <c r="AR143">
+        <v>4.1180000000000003</v>
+      </c>
+      <c r="AS143">
+        <v>5.44</v>
+      </c>
+      <c r="AT143">
+        <v>1.0660000000000001</v>
+      </c>
+      <c r="AU143">
+        <v>5.2619999999999996</v>
+      </c>
+      <c r="AV143">
+        <v>2.839</v>
+      </c>
+    </row>
+    <row r="144" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A144" s="1">
         <v>2.716656</v>
       </c>
@@ -9225,10 +12062,40 @@
       </c>
       <c r="AI144" s="1"/>
       <c r="AJ144" s="1">
-        <v>21.41602</v>
-      </c>
-    </row>
-    <row r="145" spans="1:36" x14ac:dyDescent="0.3">
+        <v>2.9</v>
+      </c>
+      <c r="AK144">
+        <v>7.077</v>
+      </c>
+      <c r="AL144">
+        <v>5.7759999999999998</v>
+      </c>
+      <c r="AM144">
+        <v>4.5339999999999998</v>
+      </c>
+      <c r="AN144">
+        <v>-1.0660000000000001</v>
+      </c>
+      <c r="AQ144">
+        <v>5.8879999999999999</v>
+      </c>
+      <c r="AR144">
+        <v>4.2789999999999999</v>
+      </c>
+      <c r="AS144">
+        <v>5.5659999999999998</v>
+      </c>
+      <c r="AT144">
+        <v>1.1950000000000001</v>
+      </c>
+      <c r="AU144">
+        <v>5.3049999999999997</v>
+      </c>
+      <c r="AV144">
+        <v>3.044</v>
+      </c>
+    </row>
+    <row r="145" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A145" s="1">
         <v>2.7333219999999998</v>
       </c>
@@ -9309,10 +12176,40 @@
       </c>
       <c r="AI145" s="1"/>
       <c r="AJ145" s="1">
-        <v>22.970300000000002</v>
-      </c>
-    </row>
-    <row r="146" spans="1:36" x14ac:dyDescent="0.3">
+        <v>2.9169999999999998</v>
+      </c>
+      <c r="AK145">
+        <v>7.0960000000000001</v>
+      </c>
+      <c r="AL145">
+        <v>5.8529999999999998</v>
+      </c>
+      <c r="AM145">
+        <v>4.5629999999999997</v>
+      </c>
+      <c r="AN145">
+        <v>-0.93200000000000005</v>
+      </c>
+      <c r="AQ145">
+        <v>5.9210000000000003</v>
+      </c>
+      <c r="AR145">
+        <v>4.4329999999999998</v>
+      </c>
+      <c r="AS145">
+        <v>5.6849999999999996</v>
+      </c>
+      <c r="AT145">
+        <v>1.3149999999999999</v>
+      </c>
+      <c r="AU145">
+        <v>5.3380000000000001</v>
+      </c>
+      <c r="AV145">
+        <v>3.234</v>
+      </c>
+    </row>
+    <row r="146" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A146" s="1">
         <v>2.7499889999999998</v>
       </c>
@@ -9393,10 +12290,16 @@
       </c>
       <c r="AI146" s="1"/>
       <c r="AJ146" s="1">
-        <v>22.27881</v>
-      </c>
-    </row>
-    <row r="147" spans="1:36" x14ac:dyDescent="0.3">
+        <v>2.9329999999999998</v>
+      </c>
+      <c r="AK146">
+        <v>7.1109999999999998</v>
+      </c>
+      <c r="AL146">
+        <v>5.9470000000000001</v>
+      </c>
+    </row>
+    <row r="147" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A147" s="1">
         <v>2.7666559999999998</v>
       </c>
@@ -9480,7 +12383,7 @@
         <v>21.880109999999998</v>
       </c>
     </row>
-    <row r="148" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A148" s="1">
         <v>2.7833220000000001</v>
       </c>
@@ -9564,7 +12467,7 @@
         <v>23.162520000000001</v>
       </c>
     </row>
-    <row r="149" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A149" s="1">
         <v>2.7999890000000001</v>
       </c>
@@ -9648,7 +12551,7 @@
         <v>21.771699999999999</v>
       </c>
     </row>
-    <row r="150" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A150" s="1">
         <v>2.8166549999999999</v>
       </c>
@@ -9732,7 +12635,7 @@
         <v>21.743130000000001</v>
       </c>
     </row>
-    <row r="151" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A151" s="1">
         <v>2.8333219999999999</v>
       </c>
@@ -9816,7 +12719,7 @@
         <v>22.821400000000001</v>
       </c>
     </row>
-    <row r="152" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A152" s="1">
         <v>2.8499889999999999</v>
       </c>
@@ -9900,7 +12803,7 @@
         <v>21.279540000000001</v>
       </c>
     </row>
-    <row r="153" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A153" s="1">
         <v>2.8666550000000002</v>
       </c>
@@ -9984,7 +12887,7 @@
         <v>21.43817</v>
       </c>
     </row>
-    <row r="154" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A154" s="1">
         <v>2.8833220000000002</v>
       </c>
@@ -10068,7 +12971,7 @@
         <v>22.08315</v>
       </c>
     </row>
-    <row r="155" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A155" s="1">
         <v>2.899988</v>
       </c>
@@ -10152,7 +13055,7 @@
         <v>20.606110000000001</v>
       </c>
     </row>
-    <row r="156" spans="1:36" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:48" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="1">
         <v>2.916655</v>
       </c>
@@ -10236,7 +13139,7 @@
         <v>20.770720000000001</v>
       </c>
     </row>
-    <row r="157" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A157" s="1">
         <v>2.933322</v>
       </c>
@@ -10318,7 +13221,7 @@
         <v>21.037510000000001</v>
       </c>
     </row>
-    <row r="158" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A158" s="1">
         <v>2.9499879999999998</v>
       </c>
@@ -10398,7 +13301,7 @@
         <v>19.86861</v>
       </c>
     </row>
-    <row r="159" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A159" s="1">
         <v>2.9666549999999998</v>
       </c>
@@ -10478,7 +13381,7 @@
         <v>20.311340000000001</v>
       </c>
     </row>
-    <row r="160" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A160" s="1">
         <v>2.9833210000000001</v>
       </c>
@@ -12760,13 +15663,9 @@
       <c r="S192" s="1"/>
       <c r="T192" s="1"/>
       <c r="U192" s="1"/>
-      <c r="Z192" s="1">
-        <v>16.338909999999998</v>
-      </c>
+      <c r="Z192" s="1"/>
       <c r="AA192" s="1"/>
-      <c r="AB192" s="1">
-        <v>9.5702540000000003</v>
-      </c>
+      <c r="AB192" s="1"/>
       <c r="AC192" s="1"/>
     </row>
     <row r="193" spans="1:13" x14ac:dyDescent="0.3">
